--- a/hernia_followup_simulated_100_patients.xlsx
+++ b/hernia_followup_simulated_100_patients.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documentos\MASTER IA EN SANIDAD\TFM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAAD0C79-02A0-4BF5-A2EE-21E373EA95C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{07FAA849-8C98-4F1F-A9DF-49F8B67D0F8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1322" uniqueCount="317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1220" uniqueCount="304">
   <si>
     <t>patient_id</t>
   </si>
@@ -198,9 +198,6 @@
     <t>general</t>
   </si>
   <si>
-    <t>normal_recovery</t>
-  </si>
-  <si>
     <t>postoperative_pain</t>
   </si>
   <si>
@@ -342,9 +339,6 @@
     <t>P031</t>
   </si>
   <si>
-    <t>borderline_local_symptom</t>
-  </si>
-  <si>
     <t>P032</t>
   </si>
   <si>
@@ -375,9 +369,6 @@
     <t>P041</t>
   </si>
   <si>
-    <t>high_risk_asymptomatic</t>
-  </si>
-  <si>
     <t>P042</t>
   </si>
   <si>
@@ -393,9 +384,6 @@
     <t>P046</t>
   </si>
   <si>
-    <t>seroma_simple</t>
-  </si>
-  <si>
     <t>seroma; postoperative_pain</t>
   </si>
   <si>
@@ -429,9 +417,6 @@
     <t>P056</t>
   </si>
   <si>
-    <t>stable_hematoma</t>
-  </si>
-  <si>
     <t>hematoma; postoperative_pain</t>
   </si>
   <si>
@@ -459,9 +444,6 @@
     <t>P064</t>
   </si>
   <si>
-    <t>mild_wound_inflammation</t>
-  </si>
-  <si>
     <t>surgical_site_infection; postoperative_pain</t>
   </si>
   <si>
@@ -483,9 +465,6 @@
     <t>P070</t>
   </si>
   <si>
-    <t>moderate_pain_controlled</t>
-  </si>
-  <si>
     <t>P071</t>
   </si>
   <si>
@@ -501,9 +480,6 @@
     <t>P075</t>
   </si>
   <si>
-    <t>mild_urinary_symptoms</t>
-  </si>
-  <si>
     <t>P076</t>
   </si>
   <si>
@@ -513,9 +489,6 @@
     <t>P078</t>
   </si>
   <si>
-    <t>late_neuropathic_pain</t>
-  </si>
-  <si>
     <t>P079</t>
   </si>
   <si>
@@ -525,9 +498,6 @@
     <t>P081</t>
   </si>
   <si>
-    <t>urinary_retention</t>
-  </si>
-  <si>
     <t>urinary_retention; postoperative_pain</t>
   </si>
   <si>
@@ -555,9 +525,6 @@
     <t>P089</t>
   </si>
   <si>
-    <t>wound_infection_alarm</t>
-  </si>
-  <si>
     <t>P090</t>
   </si>
   <si>
@@ -576,9 +543,6 @@
     <t>P095</t>
   </si>
   <si>
-    <t>expanding_hematoma_or_bleeding</t>
-  </si>
-  <si>
     <t>P096</t>
   </si>
   <si>
@@ -589,9 +553,6 @@
   </si>
   <si>
     <t>P099</t>
-  </si>
-  <si>
-    <t>severe_uncontrolled_pain</t>
   </si>
   <si>
     <t>P100</t>
@@ -1140,7 +1101,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1191,9 +1152,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1241,8 +1199,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="SimPatientsTable" displayName="SimPatientsTable" ref="A1:AS101">
-  <tableColumns count="45">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="SimPatientsTable" displayName="SimPatientsTable" ref="A1:AQ101">
+  <tableColumns count="43">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="patient_id"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="surgery_date"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="birth_date"/>
@@ -1284,8 +1242,6 @@
     <tableColumn id="41" xr3:uid="{00000000-0010-0000-0000-000029000000}" name="unable_to_void"/>
     <tableColumn id="42" xr3:uid="{00000000-0010-0000-0000-00002A000000}" name="hours_without_voiding"/>
     <tableColumn id="43" xr3:uid="{00000000-0010-0000-0000-00002B000000}" name="suprapubic_pain"/>
-    <tableColumn id="45" xr3:uid="{00000000-0010-0000-0000-00002D000000}" name="case_group"/>
-    <tableColumn id="46" xr3:uid="{00000000-0010-0000-0000-00002E000000}" name="borderline_or_ambiguous"/>
     <tableColumn id="47" xr3:uid="{00000000-0010-0000-0000-00002F000000}" name="expected_risk_level"/>
     <tableColumn id="48" xr3:uid="{00000000-0010-0000-0000-000030000000}" name="suspected_complication"/>
   </tableColumns>
@@ -1442,7 +1398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AS101"/>
+  <dimension ref="A1:AQ101"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.796875" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -1486,13 +1442,11 @@
     <col min="39" max="39" width="21.3984375" customWidth="1"/>
     <col min="40" max="40" width="22.59765625" customWidth="1"/>
     <col min="41" max="41" width="18.796875" customWidth="1"/>
-    <col min="42" max="42" width="29" customWidth="1"/>
-    <col min="43" max="43" width="26.09765625" customWidth="1"/>
-    <col min="44" max="44" width="21.59765625" customWidth="1"/>
-    <col min="45" max="45" width="33.3984375" customWidth="1"/>
+    <col min="42" max="42" width="21.59765625" customWidth="1"/>
+    <col min="43" max="43" width="33.3984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:45" ht="27.6">
+    <row r="1" spans="1:43" ht="27.6">
       <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
@@ -1617,19 +1571,13 @@
         <v>40</v>
       </c>
       <c r="AP1" s="14" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AQ1" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="AR1" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="AS1" s="14" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="2" spans="1:45">
+    <row r="2" spans="1:43">
       <c r="A2" s="15" t="s">
         <v>46</v>
       </c>
@@ -1753,22 +1701,16 @@
       <c r="AO2">
         <v>0</v>
       </c>
-      <c r="AP2" t="s">
+      <c r="AP2" s="2">
+        <v>0</v>
+      </c>
+      <c r="AQ2" t="s">
         <v>54</v>
       </c>
-      <c r="AQ2" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR2" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS2" t="s">
+    </row>
+    <row r="3" spans="1:43">
+      <c r="A3" s="15" t="s">
         <v>55</v>
-      </c>
-    </row>
-    <row r="3" spans="1:45">
-      <c r="A3" s="15" t="s">
-        <v>56</v>
       </c>
       <c r="B3" s="1">
         <v>46102</v>
@@ -1807,16 +1749,16 @@
         <v>0</v>
       </c>
       <c r="N3" t="s">
+        <v>56</v>
+      </c>
+      <c r="O3" t="s">
         <v>57</v>
-      </c>
-      <c r="O3" t="s">
-        <v>58</v>
       </c>
       <c r="P3" t="s">
         <v>50</v>
       </c>
       <c r="Q3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="R3" s="2">
         <v>53</v>
@@ -1890,22 +1832,16 @@
       <c r="AO3">
         <v>0</v>
       </c>
-      <c r="AP3" t="s">
+      <c r="AP3" s="2">
+        <v>0</v>
+      </c>
+      <c r="AQ3" t="s">
         <v>54</v>
       </c>
-      <c r="AQ3" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR3" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS3" t="s">
-        <v>55</v>
-      </c>
     </row>
-    <row r="4" spans="1:45">
+    <row r="4" spans="1:43">
       <c r="A4" s="15" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B4" s="1">
         <v>46105</v>
@@ -1947,7 +1883,7 @@
         <v>48</v>
       </c>
       <c r="O4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="P4" t="s">
         <v>50</v>
@@ -1959,7 +1895,7 @@
         <v>41</v>
       </c>
       <c r="S4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="T4" t="s">
         <v>53</v>
@@ -2027,22 +1963,16 @@
       <c r="AO4">
         <v>0</v>
       </c>
-      <c r="AP4" t="s">
+      <c r="AP4" s="2">
+        <v>0</v>
+      </c>
+      <c r="AQ4" t="s">
         <v>54</v>
       </c>
-      <c r="AQ4" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR4" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS4" t="s">
-        <v>55</v>
-      </c>
     </row>
-    <row r="5" spans="1:45">
+    <row r="5" spans="1:43">
       <c r="A5" s="15" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B5" s="1">
         <v>46105</v>
@@ -2084,10 +2014,10 @@
         <v>48</v>
       </c>
       <c r="O5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="P5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q5" t="s">
         <v>51</v>
@@ -2164,22 +2094,16 @@
       <c r="AO5">
         <v>0</v>
       </c>
-      <c r="AP5" t="s">
+      <c r="AP5" s="2">
+        <v>0</v>
+      </c>
+      <c r="AQ5" t="s">
         <v>54</v>
       </c>
-      <c r="AQ5" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR5" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS5" t="s">
-        <v>55</v>
-      </c>
     </row>
-    <row r="6" spans="1:45">
+    <row r="6" spans="1:43">
       <c r="A6" s="15" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B6" s="1">
         <v>46107</v>
@@ -2191,7 +2115,7 @@
         <v>60</v>
       </c>
       <c r="E6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F6" s="3">
         <v>28.2</v>
@@ -2221,13 +2145,13 @@
         <v>48</v>
       </c>
       <c r="O6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="P6" t="s">
         <v>50</v>
       </c>
       <c r="Q6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R6" s="2">
         <v>30</v>
@@ -2301,22 +2225,16 @@
       <c r="AO6">
         <v>0</v>
       </c>
-      <c r="AP6" t="s">
+      <c r="AP6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AQ6" t="s">
         <v>54</v>
       </c>
-      <c r="AQ6" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR6" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS6" t="s">
-        <v>55</v>
-      </c>
     </row>
-    <row r="7" spans="1:45">
+    <row r="7" spans="1:43">
       <c r="A7" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B7" s="1">
         <v>46102</v>
@@ -2358,22 +2276,22 @@
         <v>48</v>
       </c>
       <c r="O7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="P7" t="s">
         <v>50</v>
       </c>
       <c r="Q7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R7" s="2">
         <v>47</v>
       </c>
       <c r="S7" t="s">
+        <v>68</v>
+      </c>
+      <c r="T7" t="s">
         <v>69</v>
-      </c>
-      <c r="T7" t="s">
-        <v>70</v>
       </c>
       <c r="U7" s="2">
         <v>10</v>
@@ -2438,22 +2356,16 @@
       <c r="AO7">
         <v>0</v>
       </c>
-      <c r="AP7" t="s">
+      <c r="AP7" s="2">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="s">
         <v>54</v>
       </c>
-      <c r="AQ7" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR7" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS7" t="s">
-        <v>55</v>
-      </c>
     </row>
-    <row r="8" spans="1:45">
+    <row r="8" spans="1:43">
       <c r="A8" s="15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B8" s="1">
         <v>46103</v>
@@ -2465,7 +2377,7 @@
         <v>81</v>
       </c>
       <c r="E8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F8" s="3">
         <v>32.700000000000003</v>
@@ -2495,7 +2407,7 @@
         <v>48</v>
       </c>
       <c r="O8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="P8" t="s">
         <v>50</v>
@@ -2507,7 +2419,7 @@
         <v>60</v>
       </c>
       <c r="S8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="T8" t="s">
         <v>53</v>
@@ -2575,22 +2487,16 @@
       <c r="AO8">
         <v>0</v>
       </c>
-      <c r="AP8" t="s">
+      <c r="AP8" s="2">
+        <v>0</v>
+      </c>
+      <c r="AQ8" t="s">
         <v>54</v>
       </c>
-      <c r="AQ8" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR8" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS8" t="s">
-        <v>55</v>
-      </c>
     </row>
-    <row r="9" spans="1:45">
+    <row r="9" spans="1:43">
       <c r="A9" s="15" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B9" s="1">
         <v>46104</v>
@@ -2638,13 +2544,13 @@
         <v>50</v>
       </c>
       <c r="Q9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R9" s="2">
         <v>40</v>
       </c>
       <c r="S9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T9" t="s">
         <v>53</v>
@@ -2712,22 +2618,16 @@
       <c r="AO9">
         <v>0</v>
       </c>
-      <c r="AP9" t="s">
+      <c r="AP9" s="2">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="s">
         <v>54</v>
       </c>
-      <c r="AQ9" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR9" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS9" t="s">
-        <v>55</v>
-      </c>
     </row>
-    <row r="10" spans="1:45">
+    <row r="10" spans="1:43">
       <c r="A10" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B10" s="1">
         <v>46103</v>
@@ -2766,22 +2666,22 @@
         <v>0</v>
       </c>
       <c r="N10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="O10" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="P10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R10" s="2">
         <v>35</v>
       </c>
       <c r="S10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="T10" t="s">
         <v>53</v>
@@ -2849,22 +2749,16 @@
       <c r="AO10">
         <v>0</v>
       </c>
-      <c r="AP10" t="s">
+      <c r="AP10" s="2">
+        <v>0</v>
+      </c>
+      <c r="AQ10" t="s">
         <v>54</v>
       </c>
-      <c r="AQ10" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR10" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS10" t="s">
-        <v>55</v>
-      </c>
     </row>
-    <row r="11" spans="1:45">
+    <row r="11" spans="1:43">
       <c r="A11" s="15" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B11" s="1">
         <v>46105</v>
@@ -2912,16 +2806,16 @@
         <v>50</v>
       </c>
       <c r="Q11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R11" s="2">
         <v>48</v>
       </c>
       <c r="S11" t="s">
+        <v>68</v>
+      </c>
+      <c r="T11" t="s">
         <v>69</v>
-      </c>
-      <c r="T11" t="s">
-        <v>70</v>
       </c>
       <c r="U11" s="2">
         <v>7</v>
@@ -2986,22 +2880,16 @@
       <c r="AO11">
         <v>0</v>
       </c>
-      <c r="AP11" t="s">
+      <c r="AP11" s="2">
+        <v>0</v>
+      </c>
+      <c r="AQ11" t="s">
         <v>54</v>
       </c>
-      <c r="AQ11" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR11" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS11" t="s">
-        <v>55</v>
-      </c>
     </row>
-    <row r="12" spans="1:45">
+    <row r="12" spans="1:43">
       <c r="A12" s="15" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B12" s="1">
         <v>46103</v>
@@ -3043,13 +2931,13 @@
         <v>48</v>
       </c>
       <c r="O12" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="P12" t="s">
         <v>50</v>
       </c>
       <c r="Q12" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R12" s="2">
         <v>39</v>
@@ -3058,7 +2946,7 @@
         <v>52</v>
       </c>
       <c r="T12" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="U12" s="2">
         <v>9</v>
@@ -3123,22 +3011,16 @@
       <c r="AO12">
         <v>0</v>
       </c>
-      <c r="AP12" t="s">
+      <c r="AP12" s="2">
+        <v>0</v>
+      </c>
+      <c r="AQ12" t="s">
         <v>54</v>
       </c>
-      <c r="AQ12" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR12" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS12" t="s">
-        <v>55</v>
-      </c>
     </row>
-    <row r="13" spans="1:45">
+    <row r="13" spans="1:43">
       <c r="A13" s="15" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B13" s="1">
         <v>46106</v>
@@ -3177,7 +3059,7 @@
         <v>0</v>
       </c>
       <c r="N13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O13" t="s">
         <v>49</v>
@@ -3192,7 +3074,7 @@
         <v>60</v>
       </c>
       <c r="S13" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="T13" t="s">
         <v>53</v>
@@ -3260,22 +3142,16 @@
       <c r="AO13">
         <v>0</v>
       </c>
-      <c r="AP13" t="s">
+      <c r="AP13" s="2">
+        <v>0</v>
+      </c>
+      <c r="AQ13" t="s">
         <v>54</v>
       </c>
-      <c r="AQ13" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR13" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS13" t="s">
-        <v>55</v>
-      </c>
     </row>
-    <row r="14" spans="1:45">
+    <row r="14" spans="1:43">
       <c r="A14" s="15" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B14" s="1">
         <v>46110</v>
@@ -3287,7 +3163,7 @@
         <v>34</v>
       </c>
       <c r="E14" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F14" s="3">
         <v>22.1</v>
@@ -3317,7 +3193,7 @@
         <v>48</v>
       </c>
       <c r="O14" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P14" t="s">
         <v>50</v>
@@ -3397,22 +3273,16 @@
       <c r="AO14">
         <v>0</v>
       </c>
-      <c r="AP14" t="s">
+      <c r="AP14" s="2">
+        <v>0</v>
+      </c>
+      <c r="AQ14" t="s">
         <v>54</v>
       </c>
-      <c r="AQ14" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR14" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS14" t="s">
-        <v>55</v>
-      </c>
     </row>
-    <row r="15" spans="1:45">
+    <row r="15" spans="1:43">
       <c r="A15" s="15" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B15" s="1">
         <v>46104</v>
@@ -3451,7 +3321,7 @@
         <v>0</v>
       </c>
       <c r="N15" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O15" t="s">
         <v>49</v>
@@ -3466,7 +3336,7 @@
         <v>39</v>
       </c>
       <c r="S15" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="T15" t="s">
         <v>53</v>
@@ -3534,22 +3404,16 @@
       <c r="AO15">
         <v>0</v>
       </c>
-      <c r="AP15" t="s">
+      <c r="AP15" s="2">
+        <v>0</v>
+      </c>
+      <c r="AQ15" t="s">
         <v>54</v>
       </c>
-      <c r="AQ15" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR15" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS15" t="s">
-        <v>55</v>
-      </c>
     </row>
-    <row r="16" spans="1:45">
+    <row r="16" spans="1:43">
       <c r="A16" s="15" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B16" s="1">
         <v>46102</v>
@@ -3561,7 +3425,7 @@
         <v>72</v>
       </c>
       <c r="E16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F16" s="3">
         <v>34.1</v>
@@ -3588,22 +3452,22 @@
         <v>0</v>
       </c>
       <c r="N16" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O16" t="s">
+        <v>57</v>
+      </c>
+      <c r="P16" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q16" t="s">
         <v>58</v>
-      </c>
-      <c r="P16" t="s">
-        <v>63</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>59</v>
       </c>
       <c r="R16" s="2">
         <v>52</v>
       </c>
       <c r="S16" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="T16" t="s">
         <v>53</v>
@@ -3671,22 +3535,16 @@
       <c r="AO16">
         <v>0</v>
       </c>
-      <c r="AP16" t="s">
+      <c r="AP16" s="2">
+        <v>0</v>
+      </c>
+      <c r="AQ16" t="s">
         <v>54</v>
       </c>
-      <c r="AQ16" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR16" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS16" t="s">
-        <v>55</v>
-      </c>
     </row>
-    <row r="17" spans="1:45">
+    <row r="17" spans="1:43">
       <c r="A17" s="15" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B17" s="1">
         <v>46106</v>
@@ -3698,7 +3556,7 @@
         <v>79</v>
       </c>
       <c r="E17" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F17" s="3">
         <v>23.6</v>
@@ -3725,7 +3583,7 @@
         <v>0</v>
       </c>
       <c r="N17" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="O17" t="s">
         <v>49</v>
@@ -3740,7 +3598,7 @@
         <v>66</v>
       </c>
       <c r="S17" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="T17" t="s">
         <v>53</v>
@@ -3808,22 +3666,16 @@
       <c r="AO17">
         <v>0</v>
       </c>
-      <c r="AP17" t="s">
+      <c r="AP17" s="2">
+        <v>0</v>
+      </c>
+      <c r="AQ17" t="s">
         <v>54</v>
       </c>
-      <c r="AQ17" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR17" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS17" t="s">
-        <v>55</v>
-      </c>
     </row>
-    <row r="18" spans="1:45">
+    <row r="18" spans="1:43">
       <c r="A18" s="15" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B18" s="1">
         <v>46105</v>
@@ -3862,22 +3714,22 @@
         <v>0</v>
       </c>
       <c r="N18" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O18" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P18" t="s">
         <v>50</v>
       </c>
       <c r="Q18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="R18" s="2">
         <v>67</v>
       </c>
       <c r="S18" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="T18" t="s">
         <v>53</v>
@@ -3945,22 +3797,16 @@
       <c r="AO18">
         <v>0</v>
       </c>
-      <c r="AP18" t="s">
+      <c r="AP18" s="2">
+        <v>0</v>
+      </c>
+      <c r="AQ18" t="s">
         <v>54</v>
       </c>
-      <c r="AQ18" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR18" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS18" t="s">
-        <v>55</v>
-      </c>
     </row>
-    <row r="19" spans="1:45">
+    <row r="19" spans="1:43">
       <c r="A19" s="15" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B19" s="1">
         <v>46105</v>
@@ -4008,13 +3854,13 @@
         <v>50</v>
       </c>
       <c r="Q19" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R19" s="2">
         <v>38</v>
       </c>
       <c r="S19" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="T19" t="s">
         <v>53</v>
@@ -4082,22 +3928,16 @@
       <c r="AO19">
         <v>0</v>
       </c>
-      <c r="AP19" t="s">
+      <c r="AP19" s="2">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="s">
         <v>54</v>
       </c>
-      <c r="AQ19" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR19" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS19" t="s">
-        <v>55</v>
-      </c>
     </row>
-    <row r="20" spans="1:45">
+    <row r="20" spans="1:43">
       <c r="A20" s="15" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B20" s="1">
         <v>46109</v>
@@ -4151,7 +3991,7 @@
         <v>49</v>
       </c>
       <c r="S20" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="T20" t="s">
         <v>53</v>
@@ -4219,22 +4059,16 @@
       <c r="AO20">
         <v>0</v>
       </c>
-      <c r="AP20" t="s">
+      <c r="AP20" s="2">
+        <v>0</v>
+      </c>
+      <c r="AQ20" t="s">
         <v>54</v>
       </c>
-      <c r="AQ20" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR20" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS20" t="s">
-        <v>55</v>
-      </c>
     </row>
-    <row r="21" spans="1:45">
+    <row r="21" spans="1:43">
       <c r="A21" s="15" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B21" s="1">
         <v>46108</v>
@@ -4273,22 +4107,22 @@
         <v>1</v>
       </c>
       <c r="N21" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O21" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="P21" t="s">
         <v>50</v>
       </c>
       <c r="Q21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R21" s="2">
         <v>28</v>
       </c>
       <c r="S21" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="T21" t="s">
         <v>53</v>
@@ -4356,22 +4190,16 @@
       <c r="AO21">
         <v>0</v>
       </c>
-      <c r="AP21" t="s">
+      <c r="AP21" s="2">
+        <v>0</v>
+      </c>
+      <c r="AQ21" t="s">
         <v>54</v>
       </c>
-      <c r="AQ21" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR21" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS21" t="s">
-        <v>55</v>
-      </c>
     </row>
-    <row r="22" spans="1:45">
+    <row r="22" spans="1:43">
       <c r="A22" s="15" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B22" s="1">
         <v>46105</v>
@@ -4419,16 +4247,16 @@
         <v>50</v>
       </c>
       <c r="Q22" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R22" s="2">
         <v>36</v>
       </c>
       <c r="S22" t="s">
+        <v>68</v>
+      </c>
+      <c r="T22" t="s">
         <v>69</v>
-      </c>
-      <c r="T22" t="s">
-        <v>70</v>
       </c>
       <c r="U22" s="2">
         <v>7</v>
@@ -4493,22 +4321,16 @@
       <c r="AO22">
         <v>0</v>
       </c>
-      <c r="AP22" t="s">
+      <c r="AP22" s="2">
+        <v>0</v>
+      </c>
+      <c r="AQ22" t="s">
         <v>54</v>
       </c>
-      <c r="AQ22" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR22" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS22" t="s">
-        <v>55</v>
-      </c>
     </row>
-    <row r="23" spans="1:45">
+    <row r="23" spans="1:43">
       <c r="A23" s="15" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B23" s="1">
         <v>46110</v>
@@ -4547,7 +4369,7 @@
         <v>0</v>
       </c>
       <c r="N23" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="O23" t="s">
         <v>49</v>
@@ -4556,13 +4378,13 @@
         <v>50</v>
       </c>
       <c r="Q23" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="R23" s="2">
         <v>41</v>
       </c>
       <c r="S23" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="T23" t="s">
         <v>53</v>
@@ -4630,22 +4452,16 @@
       <c r="AO23">
         <v>0</v>
       </c>
-      <c r="AP23" t="s">
+      <c r="AP23" s="2">
+        <v>0</v>
+      </c>
+      <c r="AQ23" t="s">
         <v>54</v>
       </c>
-      <c r="AQ23" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR23" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS23" t="s">
-        <v>55</v>
-      </c>
     </row>
-    <row r="24" spans="1:45">
+    <row r="24" spans="1:43">
       <c r="A24" s="15" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B24" s="1">
         <v>46102</v>
@@ -4699,7 +4515,7 @@
         <v>52</v>
       </c>
       <c r="S24" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="T24" t="s">
         <v>53</v>
@@ -4767,22 +4583,16 @@
       <c r="AO24">
         <v>0</v>
       </c>
-      <c r="AP24" t="s">
+      <c r="AP24" s="2">
+        <v>0</v>
+      </c>
+      <c r="AQ24" t="s">
         <v>54</v>
       </c>
-      <c r="AQ24" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR24" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS24" t="s">
-        <v>55</v>
-      </c>
     </row>
-    <row r="25" spans="1:45">
+    <row r="25" spans="1:43">
       <c r="A25" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B25" s="1">
         <v>46106</v>
@@ -4821,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="N25" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O25" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P25" t="s">
         <v>50</v>
@@ -4836,7 +4646,7 @@
         <v>70</v>
       </c>
       <c r="S25" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="T25" t="s">
         <v>53</v>
@@ -4904,22 +4714,16 @@
       <c r="AO25">
         <v>0</v>
       </c>
-      <c r="AP25" t="s">
+      <c r="AP25" s="2">
+        <v>0</v>
+      </c>
+      <c r="AQ25" t="s">
         <v>54</v>
       </c>
-      <c r="AQ25" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR25" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS25" t="s">
-        <v>55</v>
-      </c>
     </row>
-    <row r="26" spans="1:45">
+    <row r="26" spans="1:43">
       <c r="A26" s="15" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B26" s="1">
         <v>46109</v>
@@ -4958,7 +4762,7 @@
         <v>1</v>
       </c>
       <c r="N26" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O26" t="s">
         <v>49</v>
@@ -4967,13 +4771,13 @@
         <v>50</v>
       </c>
       <c r="Q26" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="R26" s="2">
         <v>38</v>
       </c>
       <c r="S26" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="T26" t="s">
         <v>53</v>
@@ -5041,22 +4845,16 @@
       <c r="AO26">
         <v>0</v>
       </c>
-      <c r="AP26" t="s">
+      <c r="AP26" s="2">
+        <v>0</v>
+      </c>
+      <c r="AQ26" t="s">
         <v>54</v>
       </c>
-      <c r="AQ26" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR26" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS26" t="s">
-        <v>55</v>
-      </c>
     </row>
-    <row r="27" spans="1:45">
+    <row r="27" spans="1:43">
       <c r="A27" s="15" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B27" s="1">
         <v>46110</v>
@@ -5095,7 +4893,7 @@
         <v>0</v>
       </c>
       <c r="N27" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="O27" t="s">
         <v>49</v>
@@ -5104,13 +4902,13 @@
         <v>50</v>
       </c>
       <c r="Q27" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="R27" s="2">
         <v>38</v>
       </c>
       <c r="S27" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="T27" t="s">
         <v>53</v>
@@ -5178,22 +4976,16 @@
       <c r="AO27">
         <v>0</v>
       </c>
-      <c r="AP27" t="s">
+      <c r="AP27" s="2">
+        <v>0</v>
+      </c>
+      <c r="AQ27" t="s">
         <v>54</v>
       </c>
-      <c r="AQ27" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR27" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS27" t="s">
-        <v>55</v>
-      </c>
     </row>
-    <row r="28" spans="1:45">
+    <row r="28" spans="1:43">
       <c r="A28" s="15" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B28" s="1">
         <v>46103</v>
@@ -5235,19 +5027,19 @@
         <v>48</v>
       </c>
       <c r="O28" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P28" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q28" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R28" s="2">
         <v>54</v>
       </c>
       <c r="S28" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T28" t="s">
         <v>53</v>
@@ -5315,22 +5107,16 @@
       <c r="AO28">
         <v>0</v>
       </c>
-      <c r="AP28" t="s">
+      <c r="AP28" s="2">
+        <v>0</v>
+      </c>
+      <c r="AQ28" t="s">
         <v>54</v>
       </c>
-      <c r="AQ28" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR28" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS28" t="s">
-        <v>55</v>
-      </c>
     </row>
-    <row r="29" spans="1:45">
+    <row r="29" spans="1:43">
       <c r="A29" s="15" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B29" s="1">
         <v>46107</v>
@@ -5375,19 +5161,19 @@
         <v>49</v>
       </c>
       <c r="P29" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q29" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R29" s="2">
         <v>52</v>
       </c>
       <c r="S29" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T29" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="U29" s="2">
         <v>5</v>
@@ -5452,22 +5238,16 @@
       <c r="AO29">
         <v>0</v>
       </c>
-      <c r="AP29" t="s">
+      <c r="AP29" s="2">
+        <v>0</v>
+      </c>
+      <c r="AQ29" t="s">
         <v>54</v>
       </c>
-      <c r="AQ29" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR29" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS29" t="s">
-        <v>55</v>
-      </c>
     </row>
-    <row r="30" spans="1:45">
+    <row r="30" spans="1:43">
       <c r="A30" s="15" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B30" s="1">
         <v>46107</v>
@@ -5509,7 +5289,7 @@
         <v>48</v>
       </c>
       <c r="O30" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="P30" t="s">
         <v>50</v>
@@ -5521,7 +5301,7 @@
         <v>63</v>
       </c>
       <c r="S30" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="T30" t="s">
         <v>53</v>
@@ -5589,22 +5369,16 @@
       <c r="AO30">
         <v>0</v>
       </c>
-      <c r="AP30" t="s">
+      <c r="AP30" s="2">
+        <v>0</v>
+      </c>
+      <c r="AQ30" t="s">
         <v>54</v>
       </c>
-      <c r="AQ30" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR30" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS30" t="s">
-        <v>55</v>
-      </c>
     </row>
-    <row r="31" spans="1:45">
+    <row r="31" spans="1:43">
       <c r="A31" s="15" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B31" s="1">
         <v>46109</v>
@@ -5643,22 +5417,22 @@
         <v>0</v>
       </c>
       <c r="N31" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O31" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="P31" t="s">
         <v>50</v>
       </c>
       <c r="Q31" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R31" s="2">
         <v>47</v>
       </c>
       <c r="S31" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T31" t="s">
         <v>53</v>
@@ -5726,22 +5500,16 @@
       <c r="AO31">
         <v>0</v>
       </c>
-      <c r="AP31" t="s">
+      <c r="AP31" s="2">
+        <v>0</v>
+      </c>
+      <c r="AQ31" t="s">
         <v>54</v>
       </c>
-      <c r="AQ31" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR31" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS31" t="s">
-        <v>55</v>
-      </c>
     </row>
-    <row r="32" spans="1:45">
+    <row r="32" spans="1:43">
       <c r="A32" s="15" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B32" s="1">
         <v>46109</v>
@@ -5786,19 +5554,19 @@
         <v>49</v>
       </c>
       <c r="P32" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q32" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R32" s="2">
         <v>40</v>
       </c>
       <c r="S32" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="T32" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="U32" s="2">
         <v>3</v>
@@ -5863,22 +5631,16 @@
       <c r="AO32">
         <v>0</v>
       </c>
-      <c r="AP32" t="s">
-        <v>102</v>
-      </c>
-      <c r="AQ32" s="2">
-        <v>1</v>
-      </c>
-      <c r="AR32" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS32" t="s">
-        <v>55</v>
+      <c r="AP32" s="2">
+        <v>0</v>
+      </c>
+      <c r="AQ32" t="s">
+        <v>54</v>
       </c>
     </row>
-    <row r="33" spans="1:45">
+    <row r="33" spans="1:43">
       <c r="A33" s="15" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B33" s="1">
         <v>46109</v>
@@ -5917,22 +5679,22 @@
         <v>0</v>
       </c>
       <c r="N33" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O33" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="P33" t="s">
         <v>50</v>
       </c>
       <c r="Q33" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="R33" s="2">
         <v>43</v>
       </c>
       <c r="S33" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="T33" t="s">
         <v>53</v>
@@ -6000,22 +5762,16 @@
       <c r="AO33">
         <v>0</v>
       </c>
-      <c r="AP33" t="s">
+      <c r="AP33" s="2">
+        <v>0</v>
+      </c>
+      <c r="AQ33" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="34" spans="1:43">
+      <c r="A34" s="15" t="s">
         <v>102</v>
-      </c>
-      <c r="AQ33" s="2">
-        <v>1</v>
-      </c>
-      <c r="AR33" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS33" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="34" spans="1:45">
-      <c r="A34" s="15" t="s">
-        <v>104</v>
       </c>
       <c r="B34" s="1">
         <v>46109</v>
@@ -6069,7 +5825,7 @@
         <v>63</v>
       </c>
       <c r="S34" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="T34" t="s">
         <v>53</v>
@@ -6137,22 +5893,16 @@
       <c r="AO34">
         <v>0</v>
       </c>
-      <c r="AP34" t="s">
-        <v>102</v>
-      </c>
-      <c r="AQ34" s="2">
-        <v>1</v>
-      </c>
-      <c r="AR34" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS34" t="s">
-        <v>55</v>
+      <c r="AP34" s="2">
+        <v>0</v>
+      </c>
+      <c r="AQ34" t="s">
+        <v>54</v>
       </c>
     </row>
-    <row r="35" spans="1:45">
+    <row r="35" spans="1:43">
       <c r="A35" s="15" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B35" s="1">
         <v>46111</v>
@@ -6191,22 +5941,22 @@
         <v>0</v>
       </c>
       <c r="N35" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O35" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="P35" t="s">
         <v>50</v>
       </c>
       <c r="Q35" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R35" s="2">
         <v>34</v>
       </c>
       <c r="S35" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T35" t="s">
         <v>53</v>
@@ -6274,22 +6024,16 @@
       <c r="AO35">
         <v>0</v>
       </c>
-      <c r="AP35" t="s">
-        <v>102</v>
-      </c>
-      <c r="AQ35" s="2">
-        <v>1</v>
-      </c>
-      <c r="AR35" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS35" t="s">
-        <v>55</v>
+      <c r="AP35" s="2">
+        <v>0</v>
+      </c>
+      <c r="AQ35" t="s">
+        <v>54</v>
       </c>
     </row>
-    <row r="36" spans="1:45">
+    <row r="36" spans="1:43">
       <c r="A36" s="15" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B36" s="1">
         <v>46111</v>
@@ -6411,22 +6155,16 @@
       <c r="AO36">
         <v>0</v>
       </c>
-      <c r="AP36" t="s">
-        <v>102</v>
-      </c>
-      <c r="AQ36" s="2">
-        <v>1</v>
-      </c>
-      <c r="AR36" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS36" t="s">
-        <v>55</v>
+      <c r="AP36" s="2">
+        <v>0</v>
+      </c>
+      <c r="AQ36" t="s">
+        <v>54</v>
       </c>
     </row>
-    <row r="37" spans="1:45">
+    <row r="37" spans="1:43">
       <c r="A37" s="15" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B37" s="1">
         <v>46104</v>
@@ -6480,7 +6218,7 @@
         <v>42</v>
       </c>
       <c r="S37" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="T37" t="s">
         <v>53</v>
@@ -6548,22 +6286,16 @@
       <c r="AO37">
         <v>0</v>
       </c>
-      <c r="AP37" t="s">
-        <v>102</v>
-      </c>
-      <c r="AQ37" s="2">
-        <v>1</v>
-      </c>
-      <c r="AR37" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS37" t="s">
-        <v>55</v>
+      <c r="AP37" s="2">
+        <v>0</v>
+      </c>
+      <c r="AQ37" t="s">
+        <v>54</v>
       </c>
     </row>
-    <row r="38" spans="1:45">
+    <row r="38" spans="1:43">
       <c r="A38" s="15" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B38" s="1">
         <v>46108</v>
@@ -6602,22 +6334,22 @@
         <v>0</v>
       </c>
       <c r="N38" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="O38" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="P38" t="s">
         <v>50</v>
       </c>
       <c r="Q38" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="R38" s="2">
         <v>58</v>
       </c>
       <c r="S38" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="T38" t="s">
         <v>53</v>
@@ -6685,22 +6417,16 @@
       <c r="AO38">
         <v>0</v>
       </c>
-      <c r="AP38" t="s">
-        <v>102</v>
-      </c>
-      <c r="AQ38" s="2">
-        <v>1</v>
-      </c>
-      <c r="AR38" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS38" t="s">
-        <v>55</v>
+      <c r="AP38" s="2">
+        <v>0</v>
+      </c>
+      <c r="AQ38" t="s">
+        <v>54</v>
       </c>
     </row>
-    <row r="39" spans="1:45">
+    <row r="39" spans="1:43">
       <c r="A39" s="15" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B39" s="1">
         <v>46106</v>
@@ -6739,7 +6465,7 @@
         <v>0</v>
       </c>
       <c r="N39" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="O39" t="s">
         <v>49</v>
@@ -6754,7 +6480,7 @@
         <v>67</v>
       </c>
       <c r="S39" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="T39" t="s">
         <v>53</v>
@@ -6822,22 +6548,16 @@
       <c r="AO39">
         <v>0</v>
       </c>
-      <c r="AP39" t="s">
-        <v>102</v>
-      </c>
-      <c r="AQ39" s="2">
-        <v>1</v>
-      </c>
-      <c r="AR39" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS39" t="s">
-        <v>55</v>
+      <c r="AP39" s="2">
+        <v>0</v>
+      </c>
+      <c r="AQ39" t="s">
+        <v>54</v>
       </c>
     </row>
-    <row r="40" spans="1:45">
+    <row r="40" spans="1:43">
       <c r="A40" s="15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B40" s="1">
         <v>46104</v>
@@ -6876,16 +6596,16 @@
         <v>0</v>
       </c>
       <c r="N40" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="O40" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="P40" t="s">
         <v>50</v>
       </c>
       <c r="Q40" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R40" s="2">
         <v>38</v>
@@ -6894,7 +6614,7 @@
         <v>52</v>
       </c>
       <c r="T40" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="U40" s="2">
         <v>8</v>
@@ -6959,22 +6679,16 @@
       <c r="AO40">
         <v>0</v>
       </c>
-      <c r="AP40" t="s">
-        <v>102</v>
-      </c>
-      <c r="AQ40" s="2">
-        <v>1</v>
-      </c>
-      <c r="AR40" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS40" t="s">
-        <v>55</v>
+      <c r="AP40" s="2">
+        <v>0</v>
+      </c>
+      <c r="AQ40" t="s">
+        <v>54</v>
       </c>
     </row>
-    <row r="41" spans="1:45">
+    <row r="41" spans="1:43">
       <c r="A41" s="15" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B41" s="1">
         <v>46111</v>
@@ -7013,16 +6727,16 @@
         <v>0</v>
       </c>
       <c r="N41" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O41" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P41" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q41" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="R41" s="2">
         <v>78</v>
@@ -7096,22 +6810,16 @@
       <c r="AO41">
         <v>0</v>
       </c>
-      <c r="AP41" t="s">
-        <v>102</v>
-      </c>
-      <c r="AQ41" s="2">
-        <v>1</v>
-      </c>
-      <c r="AR41" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS41" t="s">
-        <v>55</v>
+      <c r="AP41" s="2">
+        <v>0</v>
+      </c>
+      <c r="AQ41" t="s">
+        <v>54</v>
       </c>
     </row>
-    <row r="42" spans="1:45">
+    <row r="42" spans="1:43">
       <c r="A42" s="15" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B42" s="1">
         <v>46108</v>
@@ -7150,7 +6858,7 @@
         <v>0</v>
       </c>
       <c r="N42" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O42" t="s">
         <v>49</v>
@@ -7159,16 +6867,16 @@
         <v>50</v>
       </c>
       <c r="Q42" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R42" s="2">
         <v>50</v>
       </c>
       <c r="S42" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="T42" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="U42" s="2">
         <v>4</v>
@@ -7233,22 +6941,16 @@
       <c r="AO42">
         <v>0</v>
       </c>
-      <c r="AP42" t="s">
-        <v>113</v>
-      </c>
-      <c r="AQ42" s="2">
-        <v>1</v>
-      </c>
-      <c r="AR42" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS42" t="s">
-        <v>55</v>
+      <c r="AP42" s="2">
+        <v>0</v>
+      </c>
+      <c r="AQ42" t="s">
+        <v>54</v>
       </c>
     </row>
-    <row r="43" spans="1:45">
+    <row r="43" spans="1:43">
       <c r="A43" s="15" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B43" s="1">
         <v>46111</v>
@@ -7290,19 +6992,19 @@
         <v>48</v>
       </c>
       <c r="O43" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="P43" t="s">
         <v>50</v>
       </c>
       <c r="Q43" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R43" s="2">
         <v>55</v>
       </c>
       <c r="S43" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T43" t="s">
         <v>53</v>
@@ -7370,22 +7072,16 @@
       <c r="AO43">
         <v>0</v>
       </c>
-      <c r="AP43" t="s">
-        <v>113</v>
-      </c>
-      <c r="AQ43" s="2">
-        <v>1</v>
-      </c>
-      <c r="AR43" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS43" t="s">
-        <v>55</v>
+      <c r="AP43" s="2">
+        <v>0</v>
+      </c>
+      <c r="AQ43" t="s">
+        <v>54</v>
       </c>
     </row>
-    <row r="44" spans="1:45">
+    <row r="44" spans="1:43">
       <c r="A44" s="15" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B44" s="1">
         <v>46109</v>
@@ -7427,13 +7123,13 @@
         <v>48</v>
       </c>
       <c r="O44" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P44" t="s">
         <v>50</v>
       </c>
       <c r="Q44" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R44" s="2">
         <v>74</v>
@@ -7507,22 +7203,16 @@
       <c r="AO44">
         <v>0</v>
       </c>
-      <c r="AP44" t="s">
+      <c r="AP44" s="2">
+        <v>0</v>
+      </c>
+      <c r="AQ44" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="45" spans="1:43">
+      <c r="A45" s="15" t="s">
         <v>113</v>
-      </c>
-      <c r="AQ44" s="2">
-        <v>1</v>
-      </c>
-      <c r="AR44" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS44" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="45" spans="1:45">
-      <c r="A45" s="15" t="s">
-        <v>116</v>
       </c>
       <c r="B45" s="1">
         <v>46108</v>
@@ -7561,13 +7251,13 @@
         <v>0</v>
       </c>
       <c r="N45" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O45" t="s">
         <v>49</v>
       </c>
       <c r="P45" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q45" t="s">
         <v>51</v>
@@ -7644,22 +7334,16 @@
       <c r="AO45">
         <v>0</v>
       </c>
-      <c r="AP45" t="s">
-        <v>113</v>
-      </c>
-      <c r="AQ45" s="2">
-        <v>1</v>
-      </c>
-      <c r="AR45" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS45" t="s">
-        <v>55</v>
+      <c r="AP45" s="2">
+        <v>0</v>
+      </c>
+      <c r="AQ45" t="s">
+        <v>54</v>
       </c>
     </row>
-    <row r="46" spans="1:45">
+    <row r="46" spans="1:43">
       <c r="A46" s="15" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B46" s="1">
         <v>46108</v>
@@ -7698,7 +7382,7 @@
         <v>0</v>
       </c>
       <c r="N46" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O46" t="s">
         <v>49</v>
@@ -7713,7 +7397,7 @@
         <v>56</v>
       </c>
       <c r="S46" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="T46" t="s">
         <v>53</v>
@@ -7781,22 +7465,16 @@
       <c r="AO46">
         <v>0</v>
       </c>
-      <c r="AP46" t="s">
-        <v>113</v>
-      </c>
-      <c r="AQ46" s="2">
-        <v>1</v>
-      </c>
-      <c r="AR46" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS46" t="s">
-        <v>55</v>
+      <c r="AP46" s="2">
+        <v>0</v>
+      </c>
+      <c r="AQ46" t="s">
+        <v>54</v>
       </c>
     </row>
-    <row r="47" spans="1:45">
+    <row r="47" spans="1:43">
       <c r="A47" s="15" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B47" s="1">
         <v>46105</v>
@@ -7808,7 +7486,7 @@
         <v>72</v>
       </c>
       <c r="E47" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F47" s="3">
         <v>34.700000000000003</v>
@@ -7835,25 +7513,25 @@
         <v>0</v>
       </c>
       <c r="N47" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O47" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P47" t="s">
         <v>50</v>
       </c>
       <c r="Q47" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R47" s="2">
         <v>65</v>
       </c>
       <c r="S47" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T47" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="U47" s="2">
         <v>7</v>
@@ -7918,22 +7596,16 @@
       <c r="AO47">
         <v>0</v>
       </c>
-      <c r="AP47" t="s">
-        <v>119</v>
-      </c>
-      <c r="AQ47" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR47" s="2">
-        <v>1</v>
-      </c>
-      <c r="AS47" t="s">
-        <v>120</v>
+      <c r="AP47" s="2">
+        <v>1</v>
+      </c>
+      <c r="AQ47" t="s">
+        <v>116</v>
       </c>
     </row>
-    <row r="48" spans="1:45">
+    <row r="48" spans="1:43">
       <c r="A48" s="15" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B48" s="1">
         <v>46108</v>
@@ -7972,25 +7644,25 @@
         <v>0</v>
       </c>
       <c r="N48" t="s">
+        <v>56</v>
+      </c>
+      <c r="O48" t="s">
         <v>57</v>
-      </c>
-      <c r="O48" t="s">
-        <v>58</v>
       </c>
       <c r="P48" t="s">
         <v>50</v>
       </c>
       <c r="Q48" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R48" s="2">
         <v>105</v>
       </c>
       <c r="S48" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T48" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="U48" s="2">
         <v>4</v>
@@ -8055,22 +7727,16 @@
       <c r="AO48">
         <v>0</v>
       </c>
-      <c r="AP48" t="s">
-        <v>119</v>
-      </c>
-      <c r="AQ48" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR48" s="2">
-        <v>1</v>
-      </c>
-      <c r="AS48" t="s">
-        <v>120</v>
+      <c r="AP48" s="2">
+        <v>1</v>
+      </c>
+      <c r="AQ48" t="s">
+        <v>116</v>
       </c>
     </row>
-    <row r="49" spans="1:45">
+    <row r="49" spans="1:43">
       <c r="A49" s="15" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="B49" s="1">
         <v>46110</v>
@@ -8109,7 +7775,7 @@
         <v>0</v>
       </c>
       <c r="N49" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="O49" t="s">
         <v>49</v>
@@ -8118,13 +7784,13 @@
         <v>50</v>
       </c>
       <c r="Q49" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R49" s="2">
         <v>32</v>
       </c>
       <c r="S49" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T49" t="s">
         <v>53</v>
@@ -8192,22 +7858,16 @@
       <c r="AO49">
         <v>0</v>
       </c>
-      <c r="AP49" t="s">
+      <c r="AP49" s="2">
+        <v>1</v>
+      </c>
+      <c r="AQ49" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="50" spans="1:43">
+      <c r="A50" s="15" t="s">
         <v>119</v>
-      </c>
-      <c r="AQ49" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR49" s="2">
-        <v>1</v>
-      </c>
-      <c r="AS49" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="50" spans="1:45">
-      <c r="A50" s="15" t="s">
-        <v>123</v>
       </c>
       <c r="B50" s="1">
         <v>46107</v>
@@ -8219,7 +7879,7 @@
         <v>82</v>
       </c>
       <c r="E50" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F50" s="3">
         <v>26.8</v>
@@ -8246,7 +7906,7 @@
         <v>0</v>
       </c>
       <c r="N50" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="O50" t="s">
         <v>49</v>
@@ -8255,16 +7915,16 @@
         <v>50</v>
       </c>
       <c r="Q50" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R50" s="2">
         <v>29</v>
       </c>
       <c r="S50" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="T50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="U50" s="2">
         <v>5</v>
@@ -8329,22 +7989,16 @@
       <c r="AO50">
         <v>0</v>
       </c>
-      <c r="AP50" t="s">
-        <v>119</v>
-      </c>
-      <c r="AQ50" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR50" s="2">
-        <v>1</v>
-      </c>
-      <c r="AS50" t="s">
+      <c r="AP50" s="2">
+        <v>1</v>
+      </c>
+      <c r="AQ50" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="51" spans="1:43">
+      <c r="A51" s="15" t="s">
         <v>120</v>
-      </c>
-    </row>
-    <row r="51" spans="1:45">
-      <c r="A51" s="15" t="s">
-        <v>124</v>
       </c>
       <c r="B51" s="1">
         <v>46108</v>
@@ -8383,7 +8037,7 @@
         <v>0</v>
       </c>
       <c r="N51" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="O51" t="s">
         <v>49</v>
@@ -8398,10 +8052,10 @@
         <v>65</v>
       </c>
       <c r="S51" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="T51" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="U51" s="2">
         <v>4</v>
@@ -8466,22 +8120,16 @@
       <c r="AO51">
         <v>0</v>
       </c>
-      <c r="AP51" t="s">
-        <v>119</v>
-      </c>
-      <c r="AQ51" s="2">
-        <v>1</v>
-      </c>
-      <c r="AR51" s="2">
-        <v>1</v>
-      </c>
-      <c r="AS51" t="s">
-        <v>120</v>
+      <c r="AP51" s="2">
+        <v>1</v>
+      </c>
+      <c r="AQ51" t="s">
+        <v>116</v>
       </c>
     </row>
-    <row r="52" spans="1:45">
+    <row r="52" spans="1:43">
       <c r="A52" s="15" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B52" s="1">
         <v>46106</v>
@@ -8520,22 +8168,22 @@
         <v>0</v>
       </c>
       <c r="N52" t="s">
+        <v>56</v>
+      </c>
+      <c r="O52" t="s">
         <v>57</v>
-      </c>
-      <c r="O52" t="s">
-        <v>58</v>
       </c>
       <c r="P52" t="s">
         <v>50</v>
       </c>
       <c r="Q52" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="R52" s="2">
         <v>38</v>
       </c>
       <c r="S52" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="T52" t="s">
         <v>53</v>
@@ -8603,22 +8251,16 @@
       <c r="AO52">
         <v>0</v>
       </c>
-      <c r="AP52" t="s">
-        <v>119</v>
-      </c>
-      <c r="AQ52" s="2">
-        <v>1</v>
-      </c>
-      <c r="AR52" s="2">
-        <v>1</v>
-      </c>
-      <c r="AS52" t="s">
-        <v>120</v>
+      <c r="AP52" s="2">
+        <v>1</v>
+      </c>
+      <c r="AQ52" t="s">
+        <v>116</v>
       </c>
     </row>
-    <row r="53" spans="1:45">
+    <row r="53" spans="1:43">
       <c r="A53" s="15" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B53" s="1">
         <v>46110</v>
@@ -8657,22 +8299,22 @@
         <v>0</v>
       </c>
       <c r="N53" t="s">
+        <v>56</v>
+      </c>
+      <c r="O53" t="s">
         <v>57</v>
-      </c>
-      <c r="O53" t="s">
-        <v>58</v>
       </c>
       <c r="P53" t="s">
         <v>50</v>
       </c>
       <c r="Q53" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R53" s="2">
         <v>37</v>
       </c>
       <c r="S53" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T53" t="s">
         <v>53</v>
@@ -8740,22 +8382,16 @@
       <c r="AO53">
         <v>0</v>
       </c>
-      <c r="AP53" t="s">
-        <v>119</v>
-      </c>
-      <c r="AQ53" s="2">
-        <v>1</v>
-      </c>
-      <c r="AR53" s="2">
-        <v>1</v>
-      </c>
-      <c r="AS53" t="s">
-        <v>120</v>
+      <c r="AP53" s="2">
+        <v>1</v>
+      </c>
+      <c r="AQ53" t="s">
+        <v>116</v>
       </c>
     </row>
-    <row r="54" spans="1:45">
+    <row r="54" spans="1:43">
       <c r="A54" s="15" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B54" s="1">
         <v>46108</v>
@@ -8794,7 +8430,7 @@
         <v>0</v>
       </c>
       <c r="N54" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="O54" t="s">
         <v>49</v>
@@ -8809,7 +8445,7 @@
         <v>36</v>
       </c>
       <c r="S54" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="T54" t="s">
         <v>53</v>
@@ -8877,22 +8513,16 @@
       <c r="AO54">
         <v>0</v>
       </c>
-      <c r="AP54" t="s">
-        <v>119</v>
-      </c>
-      <c r="AQ54" s="2">
-        <v>1</v>
-      </c>
-      <c r="AR54" s="2">
-        <v>1</v>
-      </c>
-      <c r="AS54" t="s">
-        <v>120</v>
+      <c r="AP54" s="2">
+        <v>1</v>
+      </c>
+      <c r="AQ54" t="s">
+        <v>116</v>
       </c>
     </row>
-    <row r="55" spans="1:45">
+    <row r="55" spans="1:43">
       <c r="A55" s="15" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="B55" s="1">
         <v>46107</v>
@@ -8931,25 +8561,25 @@
         <v>0</v>
       </c>
       <c r="N55" t="s">
+        <v>56</v>
+      </c>
+      <c r="O55" t="s">
         <v>57</v>
-      </c>
-      <c r="O55" t="s">
-        <v>58</v>
       </c>
       <c r="P55" t="s">
         <v>50</v>
       </c>
       <c r="Q55" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R55" s="2">
         <v>44</v>
       </c>
       <c r="S55" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T55" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="U55" s="2">
         <v>5</v>
@@ -9014,22 +8644,16 @@
       <c r="AO55">
         <v>0</v>
       </c>
-      <c r="AP55" t="s">
-        <v>119</v>
-      </c>
-      <c r="AQ55" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR55" s="2">
-        <v>1</v>
-      </c>
-      <c r="AS55" t="s">
-        <v>120</v>
+      <c r="AP55" s="2">
+        <v>1</v>
+      </c>
+      <c r="AQ55" t="s">
+        <v>116</v>
       </c>
     </row>
-    <row r="56" spans="1:45">
+    <row r="56" spans="1:43">
       <c r="A56" s="15" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B56" s="1">
         <v>46106</v>
@@ -9071,19 +8695,19 @@
         <v>48</v>
       </c>
       <c r="O56" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="P56" t="s">
         <v>50</v>
       </c>
       <c r="Q56" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="R56" s="2">
         <v>49</v>
       </c>
       <c r="S56" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="T56" t="s">
         <v>53</v>
@@ -9151,22 +8775,16 @@
       <c r="AO56">
         <v>0</v>
       </c>
-      <c r="AP56" t="s">
-        <v>119</v>
-      </c>
-      <c r="AQ56" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR56" s="2">
-        <v>1</v>
-      </c>
-      <c r="AS56" t="s">
-        <v>120</v>
+      <c r="AP56" s="2">
+        <v>1</v>
+      </c>
+      <c r="AQ56" t="s">
+        <v>116</v>
       </c>
     </row>
-    <row r="57" spans="1:45">
+    <row r="57" spans="1:43">
       <c r="A57" s="15" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B57" s="1">
         <v>46111</v>
@@ -9214,13 +8832,13 @@
         <v>50</v>
       </c>
       <c r="Q57" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R57" s="2">
         <v>57</v>
       </c>
       <c r="S57" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="T57" t="s">
         <v>53</v>
@@ -9288,22 +8906,16 @@
       <c r="AO57">
         <v>0</v>
       </c>
-      <c r="AP57" t="s">
-        <v>131</v>
-      </c>
-      <c r="AQ57" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR57" s="2">
-        <v>1</v>
-      </c>
-      <c r="AS57" t="s">
-        <v>132</v>
+      <c r="AP57" s="2">
+        <v>1</v>
+      </c>
+      <c r="AQ57" t="s">
+        <v>127</v>
       </c>
     </row>
-    <row r="58" spans="1:45">
+    <row r="58" spans="1:43">
       <c r="A58" s="15" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="B58" s="1">
         <v>46106</v>
@@ -9345,22 +8957,22 @@
         <v>48</v>
       </c>
       <c r="O58" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="P58" t="s">
         <v>50</v>
       </c>
       <c r="Q58" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R58" s="2">
         <v>43</v>
       </c>
       <c r="S58" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T58" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="U58" s="2">
         <v>6</v>
@@ -9425,22 +9037,16 @@
       <c r="AO58">
         <v>0</v>
       </c>
-      <c r="AP58" t="s">
-        <v>131</v>
-      </c>
-      <c r="AQ58" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR58" s="2">
-        <v>1</v>
-      </c>
-      <c r="AS58" t="s">
-        <v>132</v>
+      <c r="AP58" s="2">
+        <v>1</v>
+      </c>
+      <c r="AQ58" t="s">
+        <v>127</v>
       </c>
     </row>
-    <row r="59" spans="1:45">
+    <row r="59" spans="1:43">
       <c r="A59" s="15" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="B59" s="1">
         <v>46109</v>
@@ -9488,7 +9094,7 @@
         <v>50</v>
       </c>
       <c r="Q59" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R59" s="2">
         <v>55</v>
@@ -9497,7 +9103,7 @@
         <v>52</v>
       </c>
       <c r="T59" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="U59" s="2">
         <v>3</v>
@@ -9562,22 +9168,16 @@
       <c r="AO59">
         <v>0</v>
       </c>
-      <c r="AP59" t="s">
-        <v>131</v>
-      </c>
-      <c r="AQ59" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR59" s="2">
-        <v>1</v>
-      </c>
-      <c r="AS59" t="s">
-        <v>132</v>
+      <c r="AP59" s="2">
+        <v>1</v>
+      </c>
+      <c r="AQ59" t="s">
+        <v>127</v>
       </c>
     </row>
-    <row r="60" spans="1:45">
+    <row r="60" spans="1:43">
       <c r="A60" s="15" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="B60" s="1">
         <v>46110</v>
@@ -9616,22 +9216,22 @@
         <v>0</v>
       </c>
       <c r="N60" t="s">
+        <v>56</v>
+      </c>
+      <c r="O60" t="s">
         <v>57</v>
-      </c>
-      <c r="O60" t="s">
-        <v>58</v>
       </c>
       <c r="P60" t="s">
         <v>50</v>
       </c>
       <c r="Q60" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R60" s="2">
         <v>87</v>
       </c>
       <c r="S60" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T60" t="s">
         <v>53</v>
@@ -9699,22 +9299,16 @@
       <c r="AO60">
         <v>0</v>
       </c>
-      <c r="AP60" t="s">
+      <c r="AP60" s="2">
+        <v>1</v>
+      </c>
+      <c r="AQ60" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="61" spans="1:43">
+      <c r="A61" s="15" t="s">
         <v>131</v>
-      </c>
-      <c r="AQ60" s="2">
-        <v>1</v>
-      </c>
-      <c r="AR60" s="2">
-        <v>1</v>
-      </c>
-      <c r="AS60" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="61" spans="1:45">
-      <c r="A61" s="15" t="s">
-        <v>136</v>
       </c>
       <c r="B61" s="1">
         <v>46106</v>
@@ -9753,7 +9347,7 @@
         <v>0</v>
       </c>
       <c r="N61" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O61" t="s">
         <v>49</v>
@@ -9836,22 +9430,16 @@
       <c r="AO61">
         <v>0</v>
       </c>
-      <c r="AP61" t="s">
-        <v>131</v>
-      </c>
-      <c r="AQ61" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR61" s="2">
-        <v>1</v>
-      </c>
-      <c r="AS61" t="s">
+      <c r="AP61" s="2">
+        <v>1</v>
+      </c>
+      <c r="AQ61" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="62" spans="1:43">
+      <c r="A62" s="15" t="s">
         <v>132</v>
-      </c>
-    </row>
-    <row r="62" spans="1:45">
-      <c r="A62" s="15" t="s">
-        <v>137</v>
       </c>
       <c r="B62" s="1">
         <v>46106</v>
@@ -9890,25 +9478,25 @@
         <v>0</v>
       </c>
       <c r="N62" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="O62" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="P62" t="s">
         <v>50</v>
       </c>
       <c r="Q62" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R62" s="2">
         <v>36</v>
       </c>
       <c r="S62" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="T62" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="U62" s="2">
         <v>6</v>
@@ -9973,22 +9561,16 @@
       <c r="AO62">
         <v>0</v>
       </c>
-      <c r="AP62" t="s">
-        <v>131</v>
-      </c>
-      <c r="AQ62" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR62" s="2">
-        <v>1</v>
-      </c>
-      <c r="AS62" t="s">
-        <v>132</v>
+      <c r="AP62" s="2">
+        <v>1</v>
+      </c>
+      <c r="AQ62" t="s">
+        <v>127</v>
       </c>
     </row>
-    <row r="63" spans="1:45">
+    <row r="63" spans="1:43">
       <c r="A63" s="15" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="B63" s="1">
         <v>46110</v>
@@ -10036,16 +9618,16 @@
         <v>50</v>
       </c>
       <c r="Q63" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R63" s="2">
         <v>25</v>
       </c>
       <c r="S63" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T63" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="U63" s="2">
         <v>2</v>
@@ -10110,22 +9692,16 @@
       <c r="AO63">
         <v>0</v>
       </c>
-      <c r="AP63" t="s">
-        <v>131</v>
-      </c>
-      <c r="AQ63" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR63" s="2">
-        <v>1</v>
-      </c>
-      <c r="AS63" t="s">
-        <v>132</v>
+      <c r="AP63" s="2">
+        <v>1</v>
+      </c>
+      <c r="AQ63" t="s">
+        <v>127</v>
       </c>
     </row>
-    <row r="64" spans="1:45">
+    <row r="64" spans="1:43">
       <c r="A64" s="15" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="B64" s="1">
         <v>46111</v>
@@ -10173,7 +9749,7 @@
         <v>50</v>
       </c>
       <c r="Q64" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="R64" s="2">
         <v>51</v>
@@ -10247,22 +9823,16 @@
       <c r="AO64">
         <v>0</v>
       </c>
-      <c r="AP64" t="s">
-        <v>131</v>
-      </c>
-      <c r="AQ64" s="2">
-        <v>1</v>
-      </c>
-      <c r="AR64" s="2">
-        <v>1</v>
-      </c>
-      <c r="AS64" t="s">
-        <v>132</v>
+      <c r="AP64" s="2">
+        <v>1</v>
+      </c>
+      <c r="AQ64" t="s">
+        <v>127</v>
       </c>
     </row>
-    <row r="65" spans="1:45">
+    <row r="65" spans="1:43">
       <c r="A65" s="15" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="B65" s="1">
         <v>46106</v>
@@ -10304,19 +9874,19 @@
         <v>48</v>
       </c>
       <c r="O65" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="P65" t="s">
         <v>50</v>
       </c>
       <c r="Q65" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R65" s="2">
         <v>23</v>
       </c>
       <c r="S65" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="T65" t="s">
         <v>53</v>
@@ -10384,22 +9954,16 @@
       <c r="AO65">
         <v>0</v>
       </c>
-      <c r="AP65" t="s">
-        <v>141</v>
-      </c>
-      <c r="AQ65" s="2">
-        <v>1</v>
-      </c>
-      <c r="AR65" s="2">
-        <v>1</v>
-      </c>
-      <c r="AS65" t="s">
-        <v>142</v>
+      <c r="AP65" s="2">
+        <v>1</v>
+      </c>
+      <c r="AQ65" t="s">
+        <v>136</v>
       </c>
     </row>
-    <row r="66" spans="1:45">
+    <row r="66" spans="1:43">
       <c r="A66" s="15" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="B66" s="1">
         <v>46109</v>
@@ -10441,22 +10005,22 @@
         <v>48</v>
       </c>
       <c r="O66" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="P66" t="s">
         <v>50</v>
       </c>
       <c r="Q66" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R66" s="2">
         <v>42</v>
       </c>
       <c r="S66" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="T66" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="U66" s="2">
         <v>3</v>
@@ -10521,22 +10085,16 @@
       <c r="AO66">
         <v>0</v>
       </c>
-      <c r="AP66" t="s">
-        <v>141</v>
-      </c>
-      <c r="AQ66" s="2">
-        <v>1</v>
-      </c>
-      <c r="AR66" s="2">
-        <v>1</v>
-      </c>
-      <c r="AS66" t="s">
-        <v>142</v>
+      <c r="AP66" s="2">
+        <v>1</v>
+      </c>
+      <c r="AQ66" t="s">
+        <v>136</v>
       </c>
     </row>
-    <row r="67" spans="1:45">
+    <row r="67" spans="1:43">
       <c r="A67" s="15" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="B67" s="1">
         <v>46104</v>
@@ -10575,22 +10133,22 @@
         <v>1</v>
       </c>
       <c r="N67" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O67" t="s">
         <v>49</v>
       </c>
       <c r="P67" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q67" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R67" s="2">
         <v>56</v>
       </c>
       <c r="S67" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="T67" t="s">
         <v>53</v>
@@ -10658,22 +10216,16 @@
       <c r="AO67">
         <v>0</v>
       </c>
-      <c r="AP67" t="s">
-        <v>141</v>
-      </c>
-      <c r="AQ67" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR67" s="2">
-        <v>1</v>
-      </c>
-      <c r="AS67" t="s">
-        <v>142</v>
+      <c r="AP67" s="2">
+        <v>1</v>
+      </c>
+      <c r="AQ67" t="s">
+        <v>136</v>
       </c>
     </row>
-    <row r="68" spans="1:45">
+    <row r="68" spans="1:43">
       <c r="A68" s="15" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="B68" s="1">
         <v>46109</v>
@@ -10721,13 +10273,13 @@
         <v>50</v>
       </c>
       <c r="Q68" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R68" s="2">
         <v>36</v>
       </c>
       <c r="S68" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T68" t="s">
         <v>53</v>
@@ -10795,22 +10347,16 @@
       <c r="AO68">
         <v>0</v>
       </c>
-      <c r="AP68" t="s">
-        <v>141</v>
-      </c>
-      <c r="AQ68" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR68" s="2">
-        <v>1</v>
-      </c>
-      <c r="AS68" t="s">
-        <v>142</v>
+      <c r="AP68" s="2">
+        <v>1</v>
+      </c>
+      <c r="AQ68" t="s">
+        <v>136</v>
       </c>
     </row>
-    <row r="69" spans="1:45">
+    <row r="69" spans="1:43">
       <c r="A69" s="15" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="B69" s="1">
         <v>46108</v>
@@ -10849,25 +10395,25 @@
         <v>0</v>
       </c>
       <c r="N69" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O69" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="P69" t="s">
         <v>50</v>
       </c>
       <c r="Q69" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R69" s="2">
         <v>41</v>
       </c>
       <c r="S69" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T69" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="U69" s="2">
         <v>4</v>
@@ -10932,22 +10478,16 @@
       <c r="AO69">
         <v>0</v>
       </c>
-      <c r="AP69" t="s">
+      <c r="AP69" s="2">
+        <v>1</v>
+      </c>
+      <c r="AQ69" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="70" spans="1:43">
+      <c r="A70" s="15" t="s">
         <v>141</v>
-      </c>
-      <c r="AQ69" s="2">
-        <v>1</v>
-      </c>
-      <c r="AR69" s="2">
-        <v>1</v>
-      </c>
-      <c r="AS69" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="70" spans="1:45">
-      <c r="A70" s="15" t="s">
-        <v>147</v>
       </c>
       <c r="B70" s="1">
         <v>46109</v>
@@ -10986,7 +10526,7 @@
         <v>0</v>
       </c>
       <c r="N70" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O70" t="s">
         <v>49</v>
@@ -11069,22 +10609,16 @@
       <c r="AO70">
         <v>0</v>
       </c>
-      <c r="AP70" t="s">
-        <v>141</v>
-      </c>
-      <c r="AQ70" s="2">
-        <v>1</v>
-      </c>
-      <c r="AR70" s="2">
-        <v>1</v>
-      </c>
-      <c r="AS70" t="s">
+      <c r="AP70" s="2">
+        <v>1</v>
+      </c>
+      <c r="AQ70" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="71" spans="1:43">
+      <c r="A71" s="15" t="s">
         <v>142</v>
-      </c>
-    </row>
-    <row r="71" spans="1:45">
-      <c r="A71" s="15" t="s">
-        <v>148</v>
       </c>
       <c r="B71" s="1">
         <v>46110</v>
@@ -11138,7 +10672,7 @@
         <v>49</v>
       </c>
       <c r="S71" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="T71" t="s">
         <v>53</v>
@@ -11206,22 +10740,16 @@
       <c r="AO71">
         <v>0</v>
       </c>
-      <c r="AP71" t="s">
-        <v>149</v>
-      </c>
-      <c r="AQ71" s="2">
-        <v>1</v>
-      </c>
-      <c r="AR71" s="2">
-        <v>1</v>
-      </c>
-      <c r="AS71" t="s">
-        <v>55</v>
+      <c r="AP71" s="2">
+        <v>1</v>
+      </c>
+      <c r="AQ71" t="s">
+        <v>54</v>
       </c>
     </row>
-    <row r="72" spans="1:45">
+    <row r="72" spans="1:43">
       <c r="A72" s="15" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="B72" s="1">
         <v>46110</v>
@@ -11260,25 +10788,25 @@
         <v>0</v>
       </c>
       <c r="N72" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O72" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="P72" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q72" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R72" s="2">
         <v>48</v>
       </c>
       <c r="S72" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T72" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="U72" s="2">
         <v>2</v>
@@ -11343,22 +10871,16 @@
       <c r="AO72">
         <v>0</v>
       </c>
-      <c r="AP72" t="s">
-        <v>149</v>
-      </c>
-      <c r="AQ72" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR72" s="2">
-        <v>1</v>
-      </c>
-      <c r="AS72" t="s">
-        <v>55</v>
+      <c r="AP72" s="2">
+        <v>1</v>
+      </c>
+      <c r="AQ72" t="s">
+        <v>54</v>
       </c>
     </row>
-    <row r="73" spans="1:45">
+    <row r="73" spans="1:43">
       <c r="A73" s="15" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="B73" s="1">
         <v>46107</v>
@@ -11397,7 +10919,7 @@
         <v>0</v>
       </c>
       <c r="N73" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O73" t="s">
         <v>49</v>
@@ -11406,16 +10928,16 @@
         <v>50</v>
       </c>
       <c r="Q73" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R73" s="2">
         <v>35</v>
       </c>
       <c r="S73" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="T73" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="U73" s="2">
         <v>5</v>
@@ -11480,22 +11002,16 @@
       <c r="AO73">
         <v>0</v>
       </c>
-      <c r="AP73" t="s">
-        <v>149</v>
-      </c>
-      <c r="AQ73" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR73" s="2">
-        <v>1</v>
-      </c>
-      <c r="AS73" t="s">
-        <v>55</v>
+      <c r="AP73" s="2">
+        <v>1</v>
+      </c>
+      <c r="AQ73" t="s">
+        <v>54</v>
       </c>
     </row>
-    <row r="74" spans="1:45">
+    <row r="74" spans="1:43">
       <c r="A74" s="15" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="B74" s="1">
         <v>46107</v>
@@ -11507,7 +11023,7 @@
         <v>37</v>
       </c>
       <c r="E74" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F74" s="3">
         <v>23.5</v>
@@ -11537,19 +11053,19 @@
         <v>48</v>
       </c>
       <c r="O74" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P74" t="s">
         <v>50</v>
       </c>
       <c r="Q74" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R74" s="2">
         <v>68</v>
       </c>
       <c r="S74" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T74" t="s">
         <v>53</v>
@@ -11617,22 +11133,16 @@
       <c r="AO74">
         <v>0</v>
       </c>
-      <c r="AP74" t="s">
-        <v>149</v>
-      </c>
-      <c r="AQ74" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR74" s="2">
-        <v>1</v>
-      </c>
-      <c r="AS74" t="s">
-        <v>55</v>
+      <c r="AP74" s="2">
+        <v>1</v>
+      </c>
+      <c r="AQ74" t="s">
+        <v>54</v>
       </c>
     </row>
-    <row r="75" spans="1:45">
+    <row r="75" spans="1:43">
       <c r="A75" s="15" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="B75" s="1">
         <v>46107</v>
@@ -11644,7 +11154,7 @@
         <v>58</v>
       </c>
       <c r="E75" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F75" s="3">
         <v>24.6</v>
@@ -11671,7 +11181,7 @@
         <v>0</v>
       </c>
       <c r="N75" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O75" t="s">
         <v>49</v>
@@ -11680,13 +11190,13 @@
         <v>50</v>
       </c>
       <c r="Q75" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="R75" s="2">
         <v>61</v>
       </c>
       <c r="S75" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="T75" t="s">
         <v>53</v>
@@ -11754,22 +11264,16 @@
       <c r="AO75">
         <v>0</v>
       </c>
-      <c r="AP75" t="s">
-        <v>149</v>
-      </c>
-      <c r="AQ75" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR75" s="2">
-        <v>1</v>
-      </c>
-      <c r="AS75" t="s">
-        <v>55</v>
+      <c r="AP75" s="2">
+        <v>1</v>
+      </c>
+      <c r="AQ75" t="s">
+        <v>54</v>
       </c>
     </row>
-    <row r="76" spans="1:45">
+    <row r="76" spans="1:43">
       <c r="A76" s="15" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="B76" s="1">
         <v>46112</v>
@@ -11811,22 +11315,22 @@
         <v>48</v>
       </c>
       <c r="O76" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P76" t="s">
         <v>50</v>
       </c>
       <c r="Q76" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R76" s="2">
         <v>78</v>
       </c>
       <c r="S76" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="T76" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="U76" s="2">
         <v>0</v>
@@ -11891,22 +11395,16 @@
       <c r="AO76">
         <v>0</v>
       </c>
-      <c r="AP76" t="s">
-        <v>155</v>
-      </c>
-      <c r="AQ76" s="2">
-        <v>1</v>
-      </c>
-      <c r="AR76" s="2">
-        <v>1</v>
-      </c>
-      <c r="AS76" t="s">
-        <v>55</v>
+      <c r="AP76" s="2">
+        <v>1</v>
+      </c>
+      <c r="AQ76" t="s">
+        <v>54</v>
       </c>
     </row>
-    <row r="77" spans="1:45">
+    <row r="77" spans="1:43">
       <c r="A77" s="15" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="B77" s="1">
         <v>46112</v>
@@ -11945,10 +11443,10 @@
         <v>0</v>
       </c>
       <c r="N77" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="O77" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P77" t="s">
         <v>50</v>
@@ -11960,7 +11458,7 @@
         <v>67</v>
       </c>
       <c r="S77" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="T77" t="s">
         <v>53</v>
@@ -12028,22 +11526,16 @@
       <c r="AO77">
         <v>0</v>
       </c>
-      <c r="AP77" t="s">
-        <v>155</v>
-      </c>
-      <c r="AQ77" s="2">
-        <v>1</v>
-      </c>
-      <c r="AR77" s="2">
-        <v>1</v>
-      </c>
-      <c r="AS77" t="s">
-        <v>55</v>
+      <c r="AP77" s="2">
+        <v>1</v>
+      </c>
+      <c r="AQ77" t="s">
+        <v>54</v>
       </c>
     </row>
-    <row r="78" spans="1:45">
+    <row r="78" spans="1:43">
       <c r="A78" s="15" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="B78" s="1">
         <v>46109</v>
@@ -12085,13 +11577,13 @@
         <v>48</v>
       </c>
       <c r="O78" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P78" t="s">
         <v>50</v>
       </c>
       <c r="Q78" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="R78" s="2">
         <v>71</v>
@@ -12165,22 +11657,16 @@
       <c r="AO78">
         <v>0</v>
       </c>
-      <c r="AP78" t="s">
-        <v>155</v>
-      </c>
-      <c r="AQ78" s="2">
-        <v>1</v>
-      </c>
-      <c r="AR78" s="2">
-        <v>1</v>
-      </c>
-      <c r="AS78" t="s">
-        <v>55</v>
+      <c r="AP78" s="2">
+        <v>1</v>
+      </c>
+      <c r="AQ78" t="s">
+        <v>54</v>
       </c>
     </row>
-    <row r="79" spans="1:45">
+    <row r="79" spans="1:43">
       <c r="A79" s="15" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="B79" s="1">
         <v>46102</v>
@@ -12192,7 +11678,7 @@
         <v>65</v>
       </c>
       <c r="E79" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F79" s="3">
         <v>25.5</v>
@@ -12219,25 +11705,25 @@
         <v>0</v>
       </c>
       <c r="N79" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="O79" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="P79" t="s">
         <v>50</v>
       </c>
       <c r="Q79" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R79" s="2">
         <v>29</v>
       </c>
       <c r="S79" t="s">
+        <v>68</v>
+      </c>
+      <c r="T79" t="s">
         <v>69</v>
-      </c>
-      <c r="T79" t="s">
-        <v>70</v>
       </c>
       <c r="U79" s="2">
         <v>10</v>
@@ -12302,22 +11788,16 @@
       <c r="AO79">
         <v>0</v>
       </c>
-      <c r="AP79" t="s">
-        <v>159</v>
-      </c>
-      <c r="AQ79" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR79" s="2">
-        <v>1</v>
-      </c>
-      <c r="AS79" t="s">
-        <v>55</v>
+      <c r="AP79" s="2">
+        <v>1</v>
+      </c>
+      <c r="AQ79" t="s">
+        <v>54</v>
       </c>
     </row>
-    <row r="80" spans="1:45">
+    <row r="80" spans="1:43">
       <c r="A80" s="15" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="B80" s="1">
         <v>46102</v>
@@ -12356,25 +11836,25 @@
         <v>0</v>
       </c>
       <c r="N80" t="s">
+        <v>56</v>
+      </c>
+      <c r="O80" t="s">
         <v>57</v>
-      </c>
-      <c r="O80" t="s">
-        <v>58</v>
       </c>
       <c r="P80" t="s">
         <v>50</v>
       </c>
       <c r="Q80" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R80" s="2">
         <v>52</v>
       </c>
       <c r="S80" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="T80" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="U80" s="2">
         <v>10</v>
@@ -12439,22 +11919,16 @@
       <c r="AO80">
         <v>0</v>
       </c>
-      <c r="AP80" t="s">
-        <v>159</v>
-      </c>
-      <c r="AQ80" s="2">
-        <v>1</v>
-      </c>
-      <c r="AR80" s="2">
-        <v>1</v>
-      </c>
-      <c r="AS80" t="s">
-        <v>55</v>
+      <c r="AP80" s="2">
+        <v>1</v>
+      </c>
+      <c r="AQ80" t="s">
+        <v>54</v>
       </c>
     </row>
-    <row r="81" spans="1:45">
+    <row r="81" spans="1:43">
       <c r="A81" s="15" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="B81" s="1">
         <v>46100</v>
@@ -12493,10 +11967,10 @@
         <v>0</v>
       </c>
       <c r="N81" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O81" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P81" t="s">
         <v>50</v>
@@ -12508,7 +11982,7 @@
         <v>68</v>
       </c>
       <c r="S81" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="T81" t="s">
         <v>53</v>
@@ -12576,22 +12050,16 @@
       <c r="AO81">
         <v>0</v>
       </c>
-      <c r="AP81" t="s">
-        <v>159</v>
-      </c>
-      <c r="AQ81" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR81" s="2">
-        <v>1</v>
-      </c>
-      <c r="AS81" t="s">
-        <v>55</v>
+      <c r="AP81" s="2">
+        <v>1</v>
+      </c>
+      <c r="AQ81" t="s">
+        <v>54</v>
       </c>
     </row>
-    <row r="82" spans="1:45">
+    <row r="82" spans="1:43">
       <c r="A82" s="15" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="B82" s="1">
         <v>46112</v>
@@ -12633,19 +12101,19 @@
         <v>48</v>
       </c>
       <c r="O82" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P82" t="s">
         <v>50</v>
       </c>
       <c r="Q82" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="R82" s="2">
         <v>76</v>
       </c>
       <c r="S82" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="T82" t="s">
         <v>53</v>
@@ -12713,22 +12181,16 @@
       <c r="AO82">
         <v>1</v>
       </c>
-      <c r="AP82" t="s">
-        <v>163</v>
-      </c>
-      <c r="AQ82" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR82" s="2">
+      <c r="AP82" s="2">
         <v>2</v>
       </c>
-      <c r="AS82" t="s">
-        <v>164</v>
+      <c r="AQ82" t="s">
+        <v>154</v>
       </c>
     </row>
-    <row r="83" spans="1:45">
+    <row r="83" spans="1:43">
       <c r="A83" s="15" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="B83" s="1">
         <v>46109</v>
@@ -12767,13 +12229,13 @@
         <v>0</v>
       </c>
       <c r="N83" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O83" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P83" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q83" t="s">
         <v>51</v>
@@ -12782,7 +12244,7 @@
         <v>81</v>
       </c>
       <c r="S83" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="T83" t="s">
         <v>53</v>
@@ -12850,22 +12312,16 @@
       <c r="AO83">
         <v>1</v>
       </c>
-      <c r="AP83" t="s">
-        <v>163</v>
-      </c>
-      <c r="AQ83" s="2">
-        <v>1</v>
-      </c>
-      <c r="AR83" s="2">
+      <c r="AP83" s="2">
         <v>2</v>
       </c>
-      <c r="AS83" t="s">
-        <v>164</v>
+      <c r="AQ83" t="s">
+        <v>154</v>
       </c>
     </row>
-    <row r="84" spans="1:45">
+    <row r="84" spans="1:43">
       <c r="A84" s="15" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="B84" s="1">
         <v>46109</v>
@@ -12904,10 +12360,10 @@
         <v>0</v>
       </c>
       <c r="N84" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O84" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="P84" t="s">
         <v>50</v>
@@ -12919,7 +12375,7 @@
         <v>47</v>
       </c>
       <c r="S84" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="T84" t="s">
         <v>53</v>
@@ -12987,22 +12443,16 @@
       <c r="AO84">
         <v>1</v>
       </c>
-      <c r="AP84" t="s">
-        <v>163</v>
-      </c>
-      <c r="AQ84" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR84" s="2">
+      <c r="AP84" s="2">
         <v>2</v>
       </c>
-      <c r="AS84" t="s">
-        <v>164</v>
+      <c r="AQ84" t="s">
+        <v>154</v>
       </c>
     </row>
-    <row r="85" spans="1:45">
+    <row r="85" spans="1:43">
       <c r="A85" s="15" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="B85" s="1">
         <v>46111</v>
@@ -13044,19 +12494,19 @@
         <v>48</v>
       </c>
       <c r="O85" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P85" t="s">
         <v>50</v>
       </c>
       <c r="Q85" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R85" s="2">
         <v>59</v>
       </c>
       <c r="S85" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T85" t="s">
         <v>53</v>
@@ -13124,22 +12574,16 @@
       <c r="AO85">
         <v>0</v>
       </c>
-      <c r="AP85" t="s">
-        <v>163</v>
-      </c>
-      <c r="AQ85" s="2">
-        <v>1</v>
-      </c>
-      <c r="AR85" s="2">
+      <c r="AP85" s="2">
         <v>2</v>
       </c>
-      <c r="AS85" t="s">
-        <v>164</v>
+      <c r="AQ85" t="s">
+        <v>154</v>
       </c>
     </row>
-    <row r="86" spans="1:45">
+    <row r="86" spans="1:43">
       <c r="A86" s="15" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="B86" s="1">
         <v>46111</v>
@@ -13181,7 +12625,7 @@
         <v>48</v>
       </c>
       <c r="O86" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="P86" t="s">
         <v>50</v>
@@ -13193,7 +12637,7 @@
         <v>75</v>
       </c>
       <c r="S86" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="T86" t="s">
         <v>53</v>
@@ -13261,22 +12705,16 @@
       <c r="AO86">
         <v>0</v>
       </c>
-      <c r="AP86" t="s">
-        <v>163</v>
-      </c>
-      <c r="AQ86" s="2">
-        <v>1</v>
-      </c>
-      <c r="AR86" s="2">
+      <c r="AP86" s="2">
         <v>2</v>
       </c>
-      <c r="AS86" t="s">
-        <v>164</v>
+      <c r="AQ86" t="s">
+        <v>154</v>
       </c>
     </row>
-    <row r="87" spans="1:45">
+    <row r="87" spans="1:43">
       <c r="A87" s="15" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="B87" s="1">
         <v>46109</v>
@@ -13321,7 +12759,7 @@
         <v>49</v>
       </c>
       <c r="P87" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q87" t="s">
         <v>51</v>
@@ -13330,7 +12768,7 @@
         <v>41</v>
       </c>
       <c r="S87" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T87" t="s">
         <v>53</v>
@@ -13398,22 +12836,16 @@
       <c r="AO87">
         <v>0</v>
       </c>
-      <c r="AP87" t="s">
-        <v>163</v>
-      </c>
-      <c r="AQ87" s="2">
-        <v>1</v>
-      </c>
-      <c r="AR87" s="2">
+      <c r="AP87" s="2">
         <v>2</v>
       </c>
-      <c r="AS87" t="s">
-        <v>164</v>
+      <c r="AQ87" t="s">
+        <v>154</v>
       </c>
     </row>
-    <row r="88" spans="1:45">
+    <row r="88" spans="1:43">
       <c r="A88" s="15" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="B88" s="1">
         <v>46112</v>
@@ -13452,10 +12884,10 @@
         <v>0</v>
       </c>
       <c r="N88" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O88" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="P88" t="s">
         <v>50</v>
@@ -13467,7 +12899,7 @@
         <v>53</v>
       </c>
       <c r="S88" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="T88" t="s">
         <v>53</v>
@@ -13535,22 +12967,16 @@
       <c r="AO88">
         <v>1</v>
       </c>
-      <c r="AP88" t="s">
-        <v>163</v>
-      </c>
-      <c r="AQ88" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR88" s="2">
+      <c r="AP88" s="2">
         <v>2</v>
       </c>
-      <c r="AS88" t="s">
-        <v>164</v>
+      <c r="AQ88" t="s">
+        <v>154</v>
       </c>
     </row>
-    <row r="89" spans="1:45">
+    <row r="89" spans="1:43">
       <c r="A89" s="15" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="B89" s="1">
         <v>46111</v>
@@ -13592,10 +13018,10 @@
         <v>48</v>
       </c>
       <c r="O89" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P89" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q89" t="s">
         <v>51</v>
@@ -13672,22 +13098,16 @@
       <c r="AO89">
         <v>1</v>
       </c>
-      <c r="AP89" t="s">
-        <v>163</v>
-      </c>
-      <c r="AQ89" s="2">
-        <v>1</v>
-      </c>
-      <c r="AR89" s="2">
+      <c r="AP89" s="2">
         <v>2</v>
       </c>
-      <c r="AS89" t="s">
-        <v>164</v>
+      <c r="AQ89" t="s">
+        <v>154</v>
       </c>
     </row>
-    <row r="90" spans="1:45">
+    <row r="90" spans="1:43">
       <c r="A90" s="15" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="B90" s="1">
         <v>46103</v>
@@ -13699,7 +13119,7 @@
         <v>69</v>
       </c>
       <c r="E90" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F90" s="3">
         <v>33.9</v>
@@ -13726,16 +13146,16 @@
         <v>0</v>
       </c>
       <c r="N90" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O90" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P90" t="s">
         <v>50</v>
       </c>
       <c r="Q90" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="R90" s="2">
         <v>72</v>
@@ -13809,22 +13229,16 @@
       <c r="AO90">
         <v>0</v>
       </c>
-      <c r="AP90" t="s">
-        <v>173</v>
-      </c>
-      <c r="AQ90" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR90" s="2">
+      <c r="AP90" s="2">
         <v>2</v>
       </c>
-      <c r="AS90" t="s">
-        <v>142</v>
+      <c r="AQ90" t="s">
+        <v>136</v>
       </c>
     </row>
-    <row r="91" spans="1:45">
+    <row r="91" spans="1:43">
       <c r="A91" s="15" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="B91" s="1">
         <v>46106</v>
@@ -13869,7 +13283,7 @@
         <v>49</v>
       </c>
       <c r="P91" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q91" t="s">
         <v>51</v>
@@ -13878,7 +13292,7 @@
         <v>49</v>
       </c>
       <c r="S91" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="T91" t="s">
         <v>53</v>
@@ -13946,22 +13360,16 @@
       <c r="AO91">
         <v>0</v>
       </c>
-      <c r="AP91" t="s">
-        <v>173</v>
-      </c>
-      <c r="AQ91" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR91" s="2">
+      <c r="AP91" s="2">
         <v>2</v>
       </c>
-      <c r="AS91" t="s">
-        <v>142</v>
+      <c r="AQ91" t="s">
+        <v>136</v>
       </c>
     </row>
-    <row r="92" spans="1:45">
+    <row r="92" spans="1:43">
       <c r="A92" s="15" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="B92" s="1">
         <v>46105</v>
@@ -14009,16 +13417,16 @@
         <v>50</v>
       </c>
       <c r="Q92" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R92" s="2">
         <v>32</v>
       </c>
       <c r="S92" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="T92" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="U92" s="2">
         <v>7</v>
@@ -14083,22 +13491,16 @@
       <c r="AO92">
         <v>0</v>
       </c>
-      <c r="AP92" t="s">
-        <v>173</v>
-      </c>
-      <c r="AQ92" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR92" s="2">
+      <c r="AP92" s="2">
         <v>2</v>
       </c>
-      <c r="AS92" t="s">
-        <v>142</v>
+      <c r="AQ92" t="s">
+        <v>136</v>
       </c>
     </row>
-    <row r="93" spans="1:45">
+    <row r="93" spans="1:43">
       <c r="A93" s="15" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="B93" s="1">
         <v>46107</v>
@@ -14137,10 +13539,10 @@
         <v>0</v>
       </c>
       <c r="N93" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O93" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="P93" t="s">
         <v>50</v>
@@ -14220,22 +13622,16 @@
       <c r="AO93">
         <v>0</v>
       </c>
-      <c r="AP93" t="s">
-        <v>173</v>
-      </c>
-      <c r="AQ93" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR93" s="2">
+      <c r="AP93" s="2">
         <v>2</v>
       </c>
-      <c r="AS93" t="s">
-        <v>142</v>
+      <c r="AQ93" t="s">
+        <v>136</v>
       </c>
     </row>
-    <row r="94" spans="1:45">
+    <row r="94" spans="1:43">
       <c r="A94" s="15" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="B94" s="1">
         <v>46106</v>
@@ -14277,7 +13673,7 @@
         <v>48</v>
       </c>
       <c r="O94" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="P94" t="s">
         <v>50</v>
@@ -14357,22 +13753,16 @@
       <c r="AO94">
         <v>0</v>
       </c>
-      <c r="AP94" t="s">
-        <v>173</v>
-      </c>
-      <c r="AQ94" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR94" s="2">
+      <c r="AP94" s="2">
         <v>2</v>
       </c>
-      <c r="AS94" t="s">
-        <v>142</v>
+      <c r="AQ94" t="s">
+        <v>136</v>
       </c>
     </row>
-    <row r="95" spans="1:45">
+    <row r="95" spans="1:43">
       <c r="A95" s="15" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="B95" s="1">
         <v>46109</v>
@@ -14411,7 +13801,7 @@
         <v>0</v>
       </c>
       <c r="N95" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O95" t="s">
         <v>49</v>
@@ -14494,22 +13884,16 @@
       <c r="AO95">
         <v>0</v>
       </c>
-      <c r="AP95" t="s">
-        <v>173</v>
-      </c>
-      <c r="AQ95" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR95" s="2">
+      <c r="AP95" s="2">
         <v>2</v>
       </c>
-      <c r="AS95" t="s">
-        <v>142</v>
+      <c r="AQ95" t="s">
+        <v>136</v>
       </c>
     </row>
-    <row r="96" spans="1:45">
+    <row r="96" spans="1:43">
       <c r="A96" s="15" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="B96" s="1">
         <v>46110</v>
@@ -14548,16 +13932,16 @@
         <v>1</v>
       </c>
       <c r="N96" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="O96" t="s">
         <v>49</v>
       </c>
       <c r="P96" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q96" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R96" s="2">
         <v>50</v>
@@ -14566,7 +13950,7 @@
         <v>52</v>
       </c>
       <c r="T96" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="U96" s="2">
         <v>2</v>
@@ -14631,22 +14015,16 @@
       <c r="AO96">
         <v>0</v>
       </c>
-      <c r="AP96" t="s">
-        <v>180</v>
-      </c>
-      <c r="AQ96" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR96" s="2">
+      <c r="AP96" s="2">
         <v>2</v>
       </c>
-      <c r="AS96" t="s">
-        <v>132</v>
+      <c r="AQ96" t="s">
+        <v>127</v>
       </c>
     </row>
-    <row r="97" spans="1:45">
+    <row r="97" spans="1:43">
       <c r="A97" s="15" t="s">
-        <v>181</v>
+        <v>169</v>
       </c>
       <c r="B97" s="1">
         <v>46109</v>
@@ -14685,22 +14063,22 @@
         <v>1</v>
       </c>
       <c r="N97" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O97" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="P97" t="s">
         <v>50</v>
       </c>
       <c r="Q97" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R97" s="2">
         <v>30</v>
       </c>
       <c r="S97" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="T97" t="s">
         <v>53</v>
@@ -14768,22 +14146,16 @@
       <c r="AO97">
         <v>0</v>
       </c>
-      <c r="AP97" t="s">
-        <v>180</v>
-      </c>
-      <c r="AQ97" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR97" s="2">
+      <c r="AP97" s="2">
         <v>2</v>
       </c>
-      <c r="AS97" t="s">
-        <v>132</v>
+      <c r="AQ97" t="s">
+        <v>127</v>
       </c>
     </row>
-    <row r="98" spans="1:45">
+    <row r="98" spans="1:43">
       <c r="A98" s="15" t="s">
-        <v>182</v>
+        <v>170</v>
       </c>
       <c r="B98" s="1">
         <v>46109</v>
@@ -14822,7 +14194,7 @@
         <v>0</v>
       </c>
       <c r="N98" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O98" t="s">
         <v>49</v>
@@ -14905,22 +14277,16 @@
       <c r="AO98">
         <v>0</v>
       </c>
-      <c r="AP98" t="s">
-        <v>180</v>
-      </c>
-      <c r="AQ98" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR98" s="2">
+      <c r="AP98" s="2">
         <v>2</v>
       </c>
-      <c r="AS98" t="s">
-        <v>132</v>
+      <c r="AQ98" t="s">
+        <v>127</v>
       </c>
     </row>
-    <row r="99" spans="1:45">
+    <row r="99" spans="1:43">
       <c r="A99" s="15" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="B99" s="1">
         <v>46109</v>
@@ -14959,13 +14325,13 @@
         <v>1</v>
       </c>
       <c r="N99" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="O99" t="s">
         <v>49</v>
       </c>
       <c r="P99" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q99" t="s">
         <v>51</v>
@@ -14974,7 +14340,7 @@
         <v>62</v>
       </c>
       <c r="S99" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="T99" t="s">
         <v>53</v>
@@ -15042,22 +14408,16 @@
       <c r="AO99">
         <v>0</v>
       </c>
-      <c r="AP99" t="s">
-        <v>180</v>
-      </c>
-      <c r="AQ99" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR99" s="2">
+      <c r="AP99" s="2">
         <v>2</v>
       </c>
-      <c r="AS99" t="s">
-        <v>132</v>
+      <c r="AQ99" t="s">
+        <v>127</v>
       </c>
     </row>
-    <row r="100" spans="1:45">
+    <row r="100" spans="1:43">
       <c r="A100" s="15" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="B100" s="1">
         <v>46108</v>
@@ -15099,13 +14459,13 @@
         <v>48</v>
       </c>
       <c r="O100" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="P100" t="s">
         <v>50</v>
       </c>
       <c r="Q100" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="R100" s="2">
         <v>29</v>
@@ -15179,22 +14539,16 @@
       <c r="AO100">
         <v>0</v>
       </c>
-      <c r="AP100" t="s">
-        <v>185</v>
-      </c>
-      <c r="AQ100" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR100" s="2">
+      <c r="AP100" s="2">
         <v>2</v>
       </c>
-      <c r="AS100" t="s">
-        <v>55</v>
+      <c r="AQ100" t="s">
+        <v>54</v>
       </c>
     </row>
-    <row r="101" spans="1:45">
+    <row r="101" spans="1:43">
       <c r="A101" s="16" t="s">
-        <v>186</v>
+        <v>173</v>
       </c>
       <c r="B101" s="17">
         <v>46109</v>
@@ -15233,7 +14587,7 @@
         <v>0</v>
       </c>
       <c r="N101" s="19" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="O101" s="19" t="s">
         <v>49</v>
@@ -15242,7 +14596,7 @@
         <v>50</v>
       </c>
       <c r="Q101" s="19" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="R101" s="18">
         <v>41</v>
@@ -15316,17 +14670,11 @@
       <c r="AO101" s="19">
         <v>0</v>
       </c>
-      <c r="AP101" s="19" t="s">
-        <v>185</v>
-      </c>
-      <c r="AQ101" s="18">
-        <v>0</v>
-      </c>
-      <c r="AR101" s="18">
+      <c r="AP101" s="18">
         <v>2</v>
       </c>
-      <c r="AS101" s="19" t="s">
-        <v>55</v>
+      <c r="AQ101" s="19" t="s">
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -15339,20 +14687,15 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AQ2:AQ101">
-    <cfRule type="expression" dxfId="3" priority="4">
-      <formula>AQ2=1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AR2:AR101">
+  <conditionalFormatting sqref="AP2:AP101">
     <cfRule type="expression" dxfId="2" priority="1">
-      <formula>AR2=0</formula>
+      <formula>AP2=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="1" priority="2">
-      <formula>AR2=1</formula>
+      <formula>AP2=1</formula>
     </cfRule>
     <cfRule type="expression" dxfId="0" priority="3">
-      <formula>AR2=2</formula>
+      <formula>AP2=2</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -15376,7 +14719,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="17.399999999999999">
       <c r="A1" s="22" t="s">
-        <v>187</v>
+        <v>174</v>
       </c>
       <c r="B1" s="23"/>
       <c r="C1" s="23"/>
@@ -15386,22 +14729,22 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="5" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -15409,19 +14752,19 @@
         <v>0</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>195</v>
+        <v>182</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>198</v>
+        <v>185</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -15429,19 +14772,19 @@
         <v>1</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>199</v>
+        <v>186</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>200</v>
+        <v>187</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>201</v>
+        <v>188</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>203</v>
+        <v>190</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="27.6">
@@ -15449,19 +14792,19 @@
         <v>2</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>204</v>
+        <v>191</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>201</v>
+        <v>188</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="27.6">
@@ -15469,19 +14812,19 @@
         <v>3</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>207</v>
+        <v>194</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>208</v>
+        <v>195</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>209</v>
+        <v>196</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>210</v>
+        <v>197</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="27.6">
@@ -15489,19 +14832,19 @@
         <v>4</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>213</v>
+        <v>200</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>214</v>
+        <v>201</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="27.6">
@@ -15509,19 +14852,19 @@
         <v>5</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>215</v>
+        <v>202</v>
       </c>
       <c r="C9" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="F9" s="9" t="s">
         <v>205</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>216</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -15529,19 +14872,19 @@
         <v>6</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>220</v>
+        <v>207</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>223</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -15552,16 +14895,16 @@
         <v>7</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>220</v>
+        <v>207</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>224</v>
+        <v>211</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -15569,19 +14912,19 @@
         <v>8</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>225</v>
+        <v>212</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>220</v>
+        <v>207</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -15589,19 +14932,19 @@
         <v>9</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>220</v>
+        <v>207</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>228</v>
+        <v>215</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -15609,19 +14952,19 @@
         <v>10</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>229</v>
+        <v>216</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>220</v>
+        <v>207</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>230</v>
+        <v>217</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>231</v>
+        <v>218</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>232</v>
+        <v>219</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -15629,19 +14972,19 @@
         <v>11</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>233</v>
+        <v>220</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>220</v>
+        <v>207</v>
       </c>
       <c r="D15" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="F15" s="9" t="s">
         <v>221</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="F15" s="9" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -15649,19 +14992,19 @@
         <v>12</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>235</v>
+        <v>222</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>220</v>
+        <v>207</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>236</v>
+        <v>223</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="27.6">
@@ -15669,19 +15012,19 @@
         <v>13</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>237</v>
+        <v>224</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="D17" s="24" t="s">
-        <v>212</v>
+        <v>225</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>199</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>316</v>
+        <v>303</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>239</v>
+        <v>226</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -15689,19 +15032,19 @@
         <v>14</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>240</v>
+        <v>227</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="D18" s="24" t="s">
-        <v>212</v>
+        <v>225</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>199</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>241</v>
+        <v>228</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>242</v>
+        <v>229</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -15709,19 +15052,19 @@
         <v>15</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>243</v>
+        <v>230</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="D19" s="24" t="s">
-        <v>212</v>
+        <v>225</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>199</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>244</v>
+        <v>231</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>245</v>
+        <v>232</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="27.6">
@@ -15729,19 +15072,19 @@
         <v>16</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>246</v>
+        <v>233</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="D20" s="24" t="s">
-        <v>212</v>
+        <v>225</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>199</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>247</v>
+        <v>234</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>248</v>
+        <v>235</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -15749,19 +15092,19 @@
         <v>17</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>249</v>
+        <v>236</v>
       </c>
       <c r="C21" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="F21" s="9" t="s">
         <v>238</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="F21" s="9" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -15769,19 +15112,19 @@
         <v>19</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>252</v>
+        <v>239</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="D22" s="24" t="s">
-        <v>212</v>
+        <v>225</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>199</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>254</v>
+        <v>241</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -15789,19 +15132,19 @@
         <v>20</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>256</v>
-      </c>
-      <c r="D23" s="24" t="s">
-        <v>208</v>
+        <v>243</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>195</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>257</v>
+        <v>244</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>258</v>
+        <v>245</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -15809,19 +15152,19 @@
         <v>21</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>259</v>
+        <v>246</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>260</v>
+        <v>247</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -15829,19 +15172,19 @@
         <v>22</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>261</v>
+        <v>248</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>262</v>
+        <v>249</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -15849,19 +15192,19 @@
         <v>23</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>263</v>
+        <v>250</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>264</v>
+        <v>251</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -15869,19 +15212,19 @@
         <v>24</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>265</v>
+        <v>252</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>266</v>
+        <v>253</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -15889,19 +15232,19 @@
         <v>25</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>267</v>
+        <v>254</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>268</v>
+        <v>255</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -15909,19 +15252,19 @@
         <v>26</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>269</v>
+        <v>256</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>270</v>
+        <v>257</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -15929,19 +15272,19 @@
         <v>27</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>272</v>
+        <v>259</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -15949,19 +15292,19 @@
         <v>28</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>273</v>
+        <v>260</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>274</v>
+        <v>261</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -15969,19 +15312,19 @@
         <v>29</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>275</v>
+        <v>262</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>276</v>
+        <v>263</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -15989,19 +15332,19 @@
         <v>30</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>277</v>
+        <v>264</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>278</v>
+        <v>265</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -16009,19 +15352,19 @@
         <v>31</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>279</v>
+        <v>266</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>280</v>
+        <v>267</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -16029,19 +15372,19 @@
         <v>32</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>281</v>
+        <v>268</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>282</v>
+        <v>269</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -16049,19 +15392,19 @@
         <v>33</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>283</v>
+        <v>270</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="F36" s="9" t="s">
-        <v>284</v>
+        <v>271</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="27.6">
@@ -16069,19 +15412,19 @@
         <v>34</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>285</v>
+        <v>272</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>286</v>
+        <v>273</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -16089,19 +15432,19 @@
         <v>35</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>287</v>
+        <v>274</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>230</v>
+        <v>217</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>288</v>
+        <v>275</v>
       </c>
       <c r="F38" s="9" t="s">
-        <v>289</v>
+        <v>276</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="27.6">
@@ -16109,19 +15452,19 @@
         <v>36</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>290</v>
+        <v>277</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="F39" s="9" t="s">
-        <v>291</v>
+        <v>278</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -16129,19 +15472,19 @@
         <v>37</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>292</v>
+        <v>279</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="F40" s="9" t="s">
-        <v>293</v>
+        <v>280</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -16149,19 +15492,19 @@
         <v>38</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>294</v>
+        <v>281</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="F41" s="9" t="s">
-        <v>295</v>
+        <v>282</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -16169,19 +15512,19 @@
         <v>39</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>296</v>
+        <v>283</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>208</v>
+        <v>195</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>297</v>
+        <v>284</v>
       </c>
       <c r="F42" s="9" t="s">
-        <v>298</v>
+        <v>285</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -16189,19 +15532,19 @@
         <v>40</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>299</v>
+        <v>286</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="F43" s="9" t="s">
-        <v>300</v>
+        <v>287</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -16209,19 +15552,19 @@
         <v>41</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>301</v>
+        <v>288</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>302</v>
+        <v>289</v>
       </c>
       <c r="D44" s="21" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>303</v>
+        <v>290</v>
       </c>
       <c r="F44" s="9" t="s">
-        <v>304</v>
+        <v>291</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="27.6">
@@ -16229,19 +15572,19 @@
         <v>42</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>305</v>
+        <v>292</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>302</v>
+        <v>289</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="F45" s="9" t="s">
-        <v>306</v>
+        <v>293</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -16249,19 +15592,19 @@
         <v>43</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>307</v>
+        <v>294</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>302</v>
+        <v>289</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>230</v>
+        <v>217</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>308</v>
+        <v>295</v>
       </c>
       <c r="F46" s="9" t="s">
-        <v>309</v>
+        <v>296</v>
       </c>
     </row>
     <row r="47" spans="1:6">
@@ -16269,19 +15612,19 @@
         <v>44</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>310</v>
+        <v>297</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>302</v>
+        <v>289</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>311</v>
+        <v>298</v>
       </c>
       <c r="F47" s="9" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="27.6">
@@ -16289,19 +15632,19 @@
         <v>45</v>
       </c>
       <c r="B48" s="11" t="s">
-        <v>313</v>
+        <v>300</v>
       </c>
       <c r="C48" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="D48" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="E48" s="11" t="s">
+        <v>301</v>
+      </c>
+      <c r="F48" s="12" t="s">
         <v>302</v>
-      </c>
-      <c r="D48" s="11" t="s">
-        <v>196</v>
-      </c>
-      <c r="E48" s="11" t="s">
-        <v>314</v>
-      </c>
-      <c r="F48" s="12" t="s">
-        <v>315</v>
       </c>
     </row>
   </sheetData>

--- a/hernia_followup_simulated_100_patients.xlsx
+++ b/hernia_followup_simulated_100_patients.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documentos\MASTER IA EN SANIDAD\TFM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{07FAA849-8C98-4F1F-A9DF-49F8B67D0F8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{94D8681B-6FED-4CC1-8E24-D227196A79F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -165,9 +165,6 @@
     <t>borderline_or_ambiguous</t>
   </si>
   <si>
-    <t>expected_risk_level</t>
-  </si>
-  <si>
     <t>suspected_complication</t>
   </si>
   <si>
@@ -946,6 +943,9 @@
   </si>
   <si>
     <t>indirect; direct; combined; inguinoscrotal; femoral</t>
+  </si>
+  <si>
+    <t>risk_level</t>
   </si>
 </sst>
 </file>
@@ -1156,7 +1156,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="3">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1175,13 +1175,6 @@
       <fill>
         <patternFill patternType="solid">
           <bgColor rgb="FFDCFCE7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFEDE9FE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1242,7 +1235,7 @@
     <tableColumn id="41" xr3:uid="{00000000-0010-0000-0000-000029000000}" name="unable_to_void"/>
     <tableColumn id="42" xr3:uid="{00000000-0010-0000-0000-00002A000000}" name="hours_without_voiding"/>
     <tableColumn id="43" xr3:uid="{00000000-0010-0000-0000-00002B000000}" name="suprapubic_pain"/>
-    <tableColumn id="47" xr3:uid="{00000000-0010-0000-0000-00002F000000}" name="expected_risk_level"/>
+    <tableColumn id="47" xr3:uid="{00000000-0010-0000-0000-00002F000000}" name="risk_level"/>
     <tableColumn id="48" xr3:uid="{00000000-0010-0000-0000-000030000000}" name="suspected_complication"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1443,7 +1436,7 @@
     <col min="40" max="40" width="22.59765625" customWidth="1"/>
     <col min="41" max="41" width="18.796875" customWidth="1"/>
     <col min="42" max="42" width="21.59765625" customWidth="1"/>
-    <col min="43" max="43" width="33.3984375" customWidth="1"/>
+    <col min="43" max="43" width="41.796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="27.6">
@@ -1571,15 +1564,15 @@
         <v>40</v>
       </c>
       <c r="AP1" s="14" t="s">
+        <v>303</v>
+      </c>
+      <c r="AQ1" s="14" t="s">
         <v>43</v>
-      </c>
-      <c r="AQ1" s="14" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:43">
       <c r="A2" s="15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B2" s="1">
         <v>46102</v>
@@ -1591,7 +1584,7 @@
         <v>29</v>
       </c>
       <c r="E2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F2" s="3">
         <v>31.8</v>
@@ -1618,25 +1611,25 @@
         <v>0</v>
       </c>
       <c r="N2" t="s">
+        <v>47</v>
+      </c>
+      <c r="O2" t="s">
         <v>48</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P2" t="s">
         <v>49</v>
       </c>
-      <c r="P2" t="s">
+      <c r="Q2" t="s">
         <v>50</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>51</v>
       </c>
       <c r="R2" s="2">
         <v>50</v>
       </c>
       <c r="S2" t="s">
+        <v>51</v>
+      </c>
+      <c r="T2" t="s">
         <v>52</v>
-      </c>
-      <c r="T2" t="s">
-        <v>53</v>
       </c>
       <c r="U2" s="2">
         <v>10</v>
@@ -1705,12 +1698,12 @@
         <v>0</v>
       </c>
       <c r="AQ2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:43">
       <c r="A3" s="15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B3" s="1">
         <v>46102</v>
@@ -1722,7 +1715,7 @@
         <v>55</v>
       </c>
       <c r="E3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F3" s="3">
         <v>25.9</v>
@@ -1749,25 +1742,25 @@
         <v>0</v>
       </c>
       <c r="N3" t="s">
+        <v>55</v>
+      </c>
+      <c r="O3" t="s">
         <v>56</v>
       </c>
-      <c r="O3" t="s">
+      <c r="P3" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q3" t="s">
         <v>57</v>
-      </c>
-      <c r="P3" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>58</v>
       </c>
       <c r="R3" s="2">
         <v>53</v>
       </c>
       <c r="S3" t="s">
+        <v>51</v>
+      </c>
+      <c r="T3" t="s">
         <v>52</v>
-      </c>
-      <c r="T3" t="s">
-        <v>53</v>
       </c>
       <c r="U3" s="2">
         <v>10</v>
@@ -1836,12 +1829,12 @@
         <v>0</v>
       </c>
       <c r="AQ3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:43">
       <c r="A4" s="15" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B4" s="1">
         <v>46105</v>
@@ -1853,7 +1846,7 @@
         <v>46</v>
       </c>
       <c r="E4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F4" s="3">
         <v>35.299999999999997</v>
@@ -1880,25 +1873,25 @@
         <v>0</v>
       </c>
       <c r="N4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="P4" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q4" t="s">
         <v>50</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>51</v>
       </c>
       <c r="R4" s="2">
         <v>41</v>
       </c>
       <c r="S4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="U4" s="2">
         <v>7</v>
@@ -1967,12 +1960,12 @@
         <v>0</v>
       </c>
       <c r="AQ4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5" spans="1:43">
       <c r="A5" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B5" s="1">
         <v>46105</v>
@@ -1984,7 +1977,7 @@
         <v>77</v>
       </c>
       <c r="E5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F5" s="3">
         <v>21.8</v>
@@ -2011,25 +2004,25 @@
         <v>0</v>
       </c>
       <c r="N5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="P5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Q5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="R5" s="2">
         <v>46</v>
       </c>
       <c r="S5" t="s">
+        <v>51</v>
+      </c>
+      <c r="T5" t="s">
         <v>52</v>
-      </c>
-      <c r="T5" t="s">
-        <v>53</v>
       </c>
       <c r="U5" s="2">
         <v>7</v>
@@ -2098,12 +2091,12 @@
         <v>0</v>
       </c>
       <c r="AQ5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:43">
       <c r="A6" s="15" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B6" s="1">
         <v>46107</v>
@@ -2115,7 +2108,7 @@
         <v>60</v>
       </c>
       <c r="E6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F6" s="3">
         <v>28.2</v>
@@ -2142,25 +2135,25 @@
         <v>0</v>
       </c>
       <c r="N6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="P6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R6" s="2">
         <v>30</v>
       </c>
       <c r="S6" t="s">
+        <v>51</v>
+      </c>
+      <c r="T6" t="s">
         <v>52</v>
-      </c>
-      <c r="T6" t="s">
-        <v>53</v>
       </c>
       <c r="U6" s="2">
         <v>5</v>
@@ -2229,12 +2222,12 @@
         <v>0</v>
       </c>
       <c r="AQ6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:43">
       <c r="A7" s="15" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B7" s="1">
         <v>46102</v>
@@ -2246,7 +2239,7 @@
         <v>28</v>
       </c>
       <c r="E7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F7" s="3">
         <v>34.799999999999997</v>
@@ -2273,25 +2266,25 @@
         <v>0</v>
       </c>
       <c r="N7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="P7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R7" s="2">
         <v>47</v>
       </c>
       <c r="S7" t="s">
+        <v>67</v>
+      </c>
+      <c r="T7" t="s">
         <v>68</v>
-      </c>
-      <c r="T7" t="s">
-        <v>69</v>
       </c>
       <c r="U7" s="2">
         <v>10</v>
@@ -2360,12 +2353,12 @@
         <v>0</v>
       </c>
       <c r="AQ7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:43">
       <c r="A8" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B8" s="1">
         <v>46103</v>
@@ -2377,7 +2370,7 @@
         <v>81</v>
       </c>
       <c r="E8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F8" s="3">
         <v>32.700000000000003</v>
@@ -2404,25 +2397,25 @@
         <v>0</v>
       </c>
       <c r="N8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="P8" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q8" t="s">
         <v>50</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>51</v>
       </c>
       <c r="R8" s="2">
         <v>60</v>
       </c>
       <c r="S8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="U8" s="2">
         <v>9</v>
@@ -2491,12 +2484,12 @@
         <v>0</v>
       </c>
       <c r="AQ8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:43">
       <c r="A9" s="15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B9" s="1">
         <v>46104</v>
@@ -2508,7 +2501,7 @@
         <v>51</v>
       </c>
       <c r="E9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F9" s="3">
         <v>27.4</v>
@@ -2535,25 +2528,25 @@
         <v>0</v>
       </c>
       <c r="N9" t="s">
+        <v>47</v>
+      </c>
+      <c r="O9" t="s">
         <v>48</v>
       </c>
-      <c r="O9" t="s">
+      <c r="P9" t="s">
         <v>49</v>
       </c>
-      <c r="P9" t="s">
-        <v>50</v>
-      </c>
       <c r="Q9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R9" s="2">
         <v>40</v>
       </c>
       <c r="S9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="U9" s="2">
         <v>8</v>
@@ -2622,12 +2615,12 @@
         <v>0</v>
       </c>
       <c r="AQ9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:43">
       <c r="A10" s="15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B10" s="1">
         <v>46103</v>
@@ -2639,7 +2632,7 @@
         <v>64</v>
       </c>
       <c r="E10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F10" s="3">
         <v>27.9</v>
@@ -2666,25 +2659,25 @@
         <v>0</v>
       </c>
       <c r="N10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="P10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Q10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R10" s="2">
         <v>35</v>
       </c>
       <c r="S10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="T10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="U10" s="2">
         <v>9</v>
@@ -2753,12 +2746,12 @@
         <v>0</v>
       </c>
       <c r="AQ10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:43">
       <c r="A11" s="15" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B11" s="1">
         <v>46105</v>
@@ -2770,7 +2763,7 @@
         <v>43</v>
       </c>
       <c r="E11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F11" s="3">
         <v>33.700000000000003</v>
@@ -2797,25 +2790,25 @@
         <v>0</v>
       </c>
       <c r="N11" t="s">
+        <v>47</v>
+      </c>
+      <c r="O11" t="s">
         <v>48</v>
       </c>
-      <c r="O11" t="s">
+      <c r="P11" t="s">
         <v>49</v>
       </c>
-      <c r="P11" t="s">
-        <v>50</v>
-      </c>
       <c r="Q11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R11" s="2">
         <v>48</v>
       </c>
       <c r="S11" t="s">
+        <v>67</v>
+      </c>
+      <c r="T11" t="s">
         <v>68</v>
-      </c>
-      <c r="T11" t="s">
-        <v>69</v>
       </c>
       <c r="U11" s="2">
         <v>7</v>
@@ -2884,12 +2877,12 @@
         <v>0</v>
       </c>
       <c r="AQ11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="12" spans="1:43">
       <c r="A12" s="15" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B12" s="1">
         <v>46103</v>
@@ -2901,7 +2894,7 @@
         <v>57</v>
       </c>
       <c r="E12" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F12" s="3">
         <v>25.1</v>
@@ -2928,25 +2921,25 @@
         <v>0</v>
       </c>
       <c r="N12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O12" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="P12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q12" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R12" s="2">
         <v>39</v>
       </c>
       <c r="S12" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="T12" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="U12" s="2">
         <v>9</v>
@@ -3015,12 +3008,12 @@
         <v>0</v>
       </c>
       <c r="AQ12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13" spans="1:43">
       <c r="A13" s="15" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B13" s="1">
         <v>46106</v>
@@ -3032,7 +3025,7 @@
         <v>43</v>
       </c>
       <c r="E13" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F13" s="3">
         <v>26.9</v>
@@ -3059,25 +3052,25 @@
         <v>0</v>
       </c>
       <c r="N13" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="O13" t="s">
+        <v>48</v>
+      </c>
+      <c r="P13" t="s">
         <v>49</v>
       </c>
-      <c r="P13" t="s">
+      <c r="Q13" t="s">
         <v>50</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>51</v>
       </c>
       <c r="R13" s="2">
         <v>60</v>
       </c>
       <c r="S13" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="T13" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="U13" s="2">
         <v>6</v>
@@ -3146,12 +3139,12 @@
         <v>0</v>
       </c>
       <c r="AQ13" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14" spans="1:43">
       <c r="A14" s="15" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B14" s="1">
         <v>46110</v>
@@ -3163,7 +3156,7 @@
         <v>34</v>
       </c>
       <c r="E14" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F14" s="3">
         <v>22.1</v>
@@ -3190,25 +3183,25 @@
         <v>0</v>
       </c>
       <c r="N14" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O14" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P14" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q14" t="s">
         <v>50</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>51</v>
       </c>
       <c r="R14" s="2">
         <v>65</v>
       </c>
       <c r="S14" t="s">
+        <v>51</v>
+      </c>
+      <c r="T14" t="s">
         <v>52</v>
-      </c>
-      <c r="T14" t="s">
-        <v>53</v>
       </c>
       <c r="U14" s="2">
         <v>2</v>
@@ -3277,12 +3270,12 @@
         <v>0</v>
       </c>
       <c r="AQ14" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="15" spans="1:43">
       <c r="A15" s="15" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B15" s="1">
         <v>46104</v>
@@ -3294,7 +3287,7 @@
         <v>63</v>
       </c>
       <c r="E15" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F15" s="3">
         <v>23.3</v>
@@ -3321,25 +3314,25 @@
         <v>0</v>
       </c>
       <c r="N15" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="O15" t="s">
+        <v>48</v>
+      </c>
+      <c r="P15" t="s">
         <v>49</v>
       </c>
-      <c r="P15" t="s">
+      <c r="Q15" t="s">
         <v>50</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>51</v>
       </c>
       <c r="R15" s="2">
         <v>39</v>
       </c>
       <c r="S15" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="T15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="U15" s="2">
         <v>8</v>
@@ -3408,12 +3401,12 @@
         <v>0</v>
       </c>
       <c r="AQ15" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="16" spans="1:43">
       <c r="A16" s="15" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B16" s="1">
         <v>46102</v>
@@ -3425,7 +3418,7 @@
         <v>72</v>
       </c>
       <c r="E16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F16" s="3">
         <v>34.1</v>
@@ -3452,25 +3445,25 @@
         <v>0</v>
       </c>
       <c r="N16" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="O16" t="s">
+        <v>56</v>
+      </c>
+      <c r="P16" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q16" t="s">
         <v>57</v>
-      </c>
-      <c r="P16" t="s">
-        <v>62</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>58</v>
       </c>
       <c r="R16" s="2">
         <v>52</v>
       </c>
       <c r="S16" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="T16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="U16" s="2">
         <v>10</v>
@@ -3539,12 +3532,12 @@
         <v>0</v>
       </c>
       <c r="AQ16" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17" spans="1:43">
       <c r="A17" s="15" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B17" s="1">
         <v>46106</v>
@@ -3556,7 +3549,7 @@
         <v>79</v>
       </c>
       <c r="E17" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F17" s="3">
         <v>23.6</v>
@@ -3583,25 +3576,25 @@
         <v>0</v>
       </c>
       <c r="N17" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O17" t="s">
+        <v>48</v>
+      </c>
+      <c r="P17" t="s">
         <v>49</v>
       </c>
-      <c r="P17" t="s">
+      <c r="Q17" t="s">
         <v>50</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>51</v>
       </c>
       <c r="R17" s="2">
         <v>66</v>
       </c>
       <c r="S17" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T17" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="U17" s="2">
         <v>6</v>
@@ -3670,12 +3663,12 @@
         <v>0</v>
       </c>
       <c r="AQ17" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="18" spans="1:43">
       <c r="A18" s="15" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B18" s="1">
         <v>46105</v>
@@ -3687,7 +3680,7 @@
         <v>53</v>
       </c>
       <c r="E18" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F18" s="3">
         <v>25.8</v>
@@ -3714,25 +3707,25 @@
         <v>0</v>
       </c>
       <c r="N18" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="O18" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P18" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q18" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="R18" s="2">
         <v>67</v>
       </c>
       <c r="S18" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T18" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="U18" s="2">
         <v>7</v>
@@ -3801,12 +3794,12 @@
         <v>0</v>
       </c>
       <c r="AQ18" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="19" spans="1:43">
       <c r="A19" s="15" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B19" s="1">
         <v>46105</v>
@@ -3818,7 +3811,7 @@
         <v>30</v>
       </c>
       <c r="E19" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F19" s="3">
         <v>31.3</v>
@@ -3845,25 +3838,25 @@
         <v>0</v>
       </c>
       <c r="N19" t="s">
+        <v>47</v>
+      </c>
+      <c r="O19" t="s">
         <v>48</v>
       </c>
-      <c r="O19" t="s">
+      <c r="P19" t="s">
         <v>49</v>
       </c>
-      <c r="P19" t="s">
-        <v>50</v>
-      </c>
       <c r="Q19" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R19" s="2">
         <v>38</v>
       </c>
       <c r="S19" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="T19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="U19" s="2">
         <v>7</v>
@@ -3932,12 +3925,12 @@
         <v>0</v>
       </c>
       <c r="AQ19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="20" spans="1:43">
       <c r="A20" s="15" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B20" s="1">
         <v>46109</v>
@@ -3949,7 +3942,7 @@
         <v>40</v>
       </c>
       <c r="E20" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F20" s="3">
         <v>27.1</v>
@@ -3976,25 +3969,25 @@
         <v>0</v>
       </c>
       <c r="N20" t="s">
+        <v>47</v>
+      </c>
+      <c r="O20" t="s">
         <v>48</v>
       </c>
-      <c r="O20" t="s">
+      <c r="P20" t="s">
         <v>49</v>
       </c>
-      <c r="P20" t="s">
+      <c r="Q20" t="s">
         <v>50</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>51</v>
       </c>
       <c r="R20" s="2">
         <v>49</v>
       </c>
       <c r="S20" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T20" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="U20" s="2">
         <v>3</v>
@@ -4063,12 +4056,12 @@
         <v>0</v>
       </c>
       <c r="AQ20" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="21" spans="1:43">
       <c r="A21" s="15" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B21" s="1">
         <v>46108</v>
@@ -4080,7 +4073,7 @@
         <v>49</v>
       </c>
       <c r="E21" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F21" s="3">
         <v>22.4</v>
@@ -4107,25 +4100,25 @@
         <v>1</v>
       </c>
       <c r="N21" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="O21" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="P21" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q21" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R21" s="2">
         <v>28</v>
       </c>
       <c r="S21" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="T21" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="U21" s="2">
         <v>4</v>
@@ -4194,12 +4187,12 @@
         <v>0</v>
       </c>
       <c r="AQ21" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="22" spans="1:43">
       <c r="A22" s="15" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B22" s="1">
         <v>46105</v>
@@ -4211,7 +4204,7 @@
         <v>34</v>
       </c>
       <c r="E22" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F22" s="3">
         <v>32.299999999999997</v>
@@ -4238,25 +4231,25 @@
         <v>0</v>
       </c>
       <c r="N22" t="s">
+        <v>47</v>
+      </c>
+      <c r="O22" t="s">
         <v>48</v>
       </c>
-      <c r="O22" t="s">
+      <c r="P22" t="s">
         <v>49</v>
       </c>
-      <c r="P22" t="s">
-        <v>50</v>
-      </c>
       <c r="Q22" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R22" s="2">
         <v>36</v>
       </c>
       <c r="S22" t="s">
+        <v>67</v>
+      </c>
+      <c r="T22" t="s">
         <v>68</v>
-      </c>
-      <c r="T22" t="s">
-        <v>69</v>
       </c>
       <c r="U22" s="2">
         <v>7</v>
@@ -4325,12 +4318,12 @@
         <v>0</v>
       </c>
       <c r="AQ22" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="23" spans="1:43">
       <c r="A23" s="15" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B23" s="1">
         <v>46110</v>
@@ -4342,7 +4335,7 @@
         <v>44</v>
       </c>
       <c r="E23" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F23" s="3">
         <v>31.9</v>
@@ -4369,25 +4362,25 @@
         <v>0</v>
       </c>
       <c r="N23" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O23" t="s">
+        <v>48</v>
+      </c>
+      <c r="P23" t="s">
         <v>49</v>
       </c>
-      <c r="P23" t="s">
-        <v>50</v>
-      </c>
       <c r="Q23" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="R23" s="2">
         <v>41</v>
       </c>
       <c r="S23" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T23" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="U23" s="2">
         <v>2</v>
@@ -4456,12 +4449,12 @@
         <v>0</v>
       </c>
       <c r="AQ23" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="24" spans="1:43">
       <c r="A24" s="15" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B24" s="1">
         <v>46102</v>
@@ -4473,7 +4466,7 @@
         <v>31</v>
       </c>
       <c r="E24" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F24" s="3">
         <v>24</v>
@@ -4500,25 +4493,25 @@
         <v>0</v>
       </c>
       <c r="N24" t="s">
+        <v>47</v>
+      </c>
+      <c r="O24" t="s">
         <v>48</v>
       </c>
-      <c r="O24" t="s">
+      <c r="P24" t="s">
         <v>49</v>
       </c>
-      <c r="P24" t="s">
+      <c r="Q24" t="s">
         <v>50</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>51</v>
       </c>
       <c r="R24" s="2">
         <v>52</v>
       </c>
       <c r="S24" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T24" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="U24" s="2">
         <v>10</v>
@@ -4587,12 +4580,12 @@
         <v>0</v>
       </c>
       <c r="AQ24" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="25" spans="1:43">
       <c r="A25" s="15" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B25" s="1">
         <v>46106</v>
@@ -4604,7 +4597,7 @@
         <v>29</v>
       </c>
       <c r="E25" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F25" s="3">
         <v>26.6</v>
@@ -4631,25 +4624,25 @@
         <v>0</v>
       </c>
       <c r="N25" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="O25" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P25" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q25" t="s">
         <v>50</v>
-      </c>
-      <c r="Q25" t="s">
-        <v>51</v>
       </c>
       <c r="R25" s="2">
         <v>70</v>
       </c>
       <c r="S25" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T25" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="U25" s="2">
         <v>6</v>
@@ -4718,12 +4711,12 @@
         <v>0</v>
       </c>
       <c r="AQ25" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="26" spans="1:43">
       <c r="A26" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B26" s="1">
         <v>46109</v>
@@ -4735,7 +4728,7 @@
         <v>52</v>
       </c>
       <c r="E26" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F26" s="3">
         <v>25</v>
@@ -4762,25 +4755,25 @@
         <v>1</v>
       </c>
       <c r="N26" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="O26" t="s">
+        <v>48</v>
+      </c>
+      <c r="P26" t="s">
         <v>49</v>
       </c>
-      <c r="P26" t="s">
-        <v>50</v>
-      </c>
       <c r="Q26" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="R26" s="2">
         <v>38</v>
       </c>
       <c r="S26" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T26" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="U26" s="2">
         <v>3</v>
@@ -4849,12 +4842,12 @@
         <v>0</v>
       </c>
       <c r="AQ26" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="27" spans="1:43">
       <c r="A27" s="15" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B27" s="1">
         <v>46110</v>
@@ -4866,7 +4859,7 @@
         <v>41</v>
       </c>
       <c r="E27" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F27" s="3">
         <v>27.7</v>
@@ -4893,25 +4886,25 @@
         <v>0</v>
       </c>
       <c r="N27" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O27" t="s">
+        <v>48</v>
+      </c>
+      <c r="P27" t="s">
         <v>49</v>
       </c>
-      <c r="P27" t="s">
-        <v>50</v>
-      </c>
       <c r="Q27" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="R27" s="2">
         <v>38</v>
       </c>
       <c r="S27" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T27" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="U27" s="2">
         <v>2</v>
@@ -4980,12 +4973,12 @@
         <v>0</v>
       </c>
       <c r="AQ27" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="28" spans="1:43">
       <c r="A28" s="15" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B28" s="1">
         <v>46103</v>
@@ -4997,7 +4990,7 @@
         <v>71</v>
       </c>
       <c r="E28" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F28" s="3">
         <v>29.7</v>
@@ -5024,25 +5017,25 @@
         <v>0</v>
       </c>
       <c r="N28" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O28" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P28" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Q28" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R28" s="2">
         <v>54</v>
       </c>
       <c r="S28" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T28" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="U28" s="2">
         <v>9</v>
@@ -5111,12 +5104,12 @@
         <v>0</v>
       </c>
       <c r="AQ28" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="29" spans="1:43">
       <c r="A29" s="15" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B29" s="1">
         <v>46107</v>
@@ -5128,7 +5121,7 @@
         <v>65</v>
       </c>
       <c r="E29" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F29" s="3">
         <v>24.9</v>
@@ -5155,25 +5148,25 @@
         <v>0</v>
       </c>
       <c r="N29" t="s">
+        <v>47</v>
+      </c>
+      <c r="O29" t="s">
         <v>48</v>
       </c>
-      <c r="O29" t="s">
-        <v>49</v>
-      </c>
       <c r="P29" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Q29" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R29" s="2">
         <v>52</v>
       </c>
       <c r="S29" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T29" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="U29" s="2">
         <v>5</v>
@@ -5242,12 +5235,12 @@
         <v>0</v>
       </c>
       <c r="AQ29" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="30" spans="1:43">
       <c r="A30" s="15" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B30" s="1">
         <v>46107</v>
@@ -5259,7 +5252,7 @@
         <v>59</v>
       </c>
       <c r="E30" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F30" s="3">
         <v>29.1</v>
@@ -5286,25 +5279,25 @@
         <v>0</v>
       </c>
       <c r="N30" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O30" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="P30" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q30" t="s">
         <v>50</v>
-      </c>
-      <c r="Q30" t="s">
-        <v>51</v>
       </c>
       <c r="R30" s="2">
         <v>63</v>
       </c>
       <c r="S30" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T30" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="U30" s="2">
         <v>5</v>
@@ -5373,12 +5366,12 @@
         <v>0</v>
       </c>
       <c r="AQ30" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="31" spans="1:43">
       <c r="A31" s="15" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B31" s="1">
         <v>46109</v>
@@ -5390,7 +5383,7 @@
         <v>48</v>
       </c>
       <c r="E31" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F31" s="3">
         <v>22.7</v>
@@ -5417,25 +5410,25 @@
         <v>0</v>
       </c>
       <c r="N31" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="O31" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="P31" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q31" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R31" s="2">
         <v>47</v>
       </c>
       <c r="S31" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T31" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="U31" s="2">
         <v>3</v>
@@ -5504,12 +5497,12 @@
         <v>0</v>
       </c>
       <c r="AQ31" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="32" spans="1:43">
       <c r="A32" s="15" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B32" s="1">
         <v>46109</v>
@@ -5521,7 +5514,7 @@
         <v>72</v>
       </c>
       <c r="E32" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F32" s="3">
         <v>34.700000000000003</v>
@@ -5548,25 +5541,25 @@
         <v>0</v>
       </c>
       <c r="N32" t="s">
+        <v>47</v>
+      </c>
+      <c r="O32" t="s">
         <v>48</v>
       </c>
-      <c r="O32" t="s">
-        <v>49</v>
-      </c>
       <c r="P32" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Q32" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R32" s="2">
         <v>40</v>
       </c>
       <c r="S32" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="T32" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="U32" s="2">
         <v>3</v>
@@ -5635,12 +5628,12 @@
         <v>0</v>
       </c>
       <c r="AQ32" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="33" spans="1:43">
       <c r="A33" s="15" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B33" s="1">
         <v>46109</v>
@@ -5652,7 +5645,7 @@
         <v>76</v>
       </c>
       <c r="E33" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F33" s="3">
         <v>27</v>
@@ -5679,25 +5672,25 @@
         <v>0</v>
       </c>
       <c r="N33" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="O33" t="s">
+        <v>56</v>
+      </c>
+      <c r="P33" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q33" t="s">
         <v>57</v>
-      </c>
-      <c r="P33" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q33" t="s">
-        <v>58</v>
       </c>
       <c r="R33" s="2">
         <v>43</v>
       </c>
       <c r="S33" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T33" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="U33" s="2">
         <v>3</v>
@@ -5766,12 +5759,12 @@
         <v>0</v>
       </c>
       <c r="AQ33" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="34" spans="1:43">
       <c r="A34" s="15" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B34" s="1">
         <v>46109</v>
@@ -5783,7 +5776,7 @@
         <v>28</v>
       </c>
       <c r="E34" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F34" s="3">
         <v>26.9</v>
@@ -5810,25 +5803,25 @@
         <v>0</v>
       </c>
       <c r="N34" t="s">
+        <v>47</v>
+      </c>
+      <c r="O34" t="s">
         <v>48</v>
       </c>
-      <c r="O34" t="s">
+      <c r="P34" t="s">
         <v>49</v>
       </c>
-      <c r="P34" t="s">
+      <c r="Q34" t="s">
         <v>50</v>
-      </c>
-      <c r="Q34" t="s">
-        <v>51</v>
       </c>
       <c r="R34" s="2">
         <v>63</v>
       </c>
       <c r="S34" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="T34" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="U34" s="2">
         <v>3</v>
@@ -5897,12 +5890,12 @@
         <v>0</v>
       </c>
       <c r="AQ34" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="35" spans="1:43">
       <c r="A35" s="15" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B35" s="1">
         <v>46111</v>
@@ -5914,7 +5907,7 @@
         <v>78</v>
       </c>
       <c r="E35" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F35" s="3">
         <v>25.5</v>
@@ -5941,25 +5934,25 @@
         <v>0</v>
       </c>
       <c r="N35" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="O35" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="P35" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q35" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R35" s="2">
         <v>34</v>
       </c>
       <c r="S35" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T35" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="U35" s="2">
         <v>1</v>
@@ -6028,12 +6021,12 @@
         <v>0</v>
       </c>
       <c r="AQ35" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="36" spans="1:43">
       <c r="A36" s="15" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B36" s="1">
         <v>46111</v>
@@ -6045,7 +6038,7 @@
         <v>39</v>
       </c>
       <c r="E36" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F36" s="3">
         <v>27.8</v>
@@ -6072,25 +6065,25 @@
         <v>0</v>
       </c>
       <c r="N36" t="s">
+        <v>47</v>
+      </c>
+      <c r="O36" t="s">
         <v>48</v>
       </c>
-      <c r="O36" t="s">
+      <c r="P36" t="s">
         <v>49</v>
       </c>
-      <c r="P36" t="s">
+      <c r="Q36" t="s">
         <v>50</v>
-      </c>
-      <c r="Q36" t="s">
-        <v>51</v>
       </c>
       <c r="R36" s="2">
         <v>37</v>
       </c>
       <c r="S36" t="s">
+        <v>51</v>
+      </c>
+      <c r="T36" t="s">
         <v>52</v>
-      </c>
-      <c r="T36" t="s">
-        <v>53</v>
       </c>
       <c r="U36" s="2">
         <v>1</v>
@@ -6159,12 +6152,12 @@
         <v>0</v>
       </c>
       <c r="AQ36" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="37" spans="1:43">
       <c r="A37" s="15" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B37" s="1">
         <v>46104</v>
@@ -6176,7 +6169,7 @@
         <v>35</v>
       </c>
       <c r="E37" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F37" s="3">
         <v>35.1</v>
@@ -6203,25 +6196,25 @@
         <v>0</v>
       </c>
       <c r="N37" t="s">
+        <v>47</v>
+      </c>
+      <c r="O37" t="s">
         <v>48</v>
       </c>
-      <c r="O37" t="s">
+      <c r="P37" t="s">
         <v>49</v>
       </c>
-      <c r="P37" t="s">
+      <c r="Q37" t="s">
         <v>50</v>
-      </c>
-      <c r="Q37" t="s">
-        <v>51</v>
       </c>
       <c r="R37" s="2">
         <v>42</v>
       </c>
       <c r="S37" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T37" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="U37" s="2">
         <v>8</v>
@@ -6290,12 +6283,12 @@
         <v>0</v>
       </c>
       <c r="AQ37" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="38" spans="1:43">
       <c r="A38" s="15" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B38" s="1">
         <v>46108</v>
@@ -6307,7 +6300,7 @@
         <v>43</v>
       </c>
       <c r="E38" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F38" s="3">
         <v>31.3</v>
@@ -6334,25 +6327,25 @@
         <v>0</v>
       </c>
       <c r="N38" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O38" t="s">
+        <v>56</v>
+      </c>
+      <c r="P38" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q38" t="s">
         <v>57</v>
-      </c>
-      <c r="P38" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q38" t="s">
-        <v>58</v>
       </c>
       <c r="R38" s="2">
         <v>58</v>
       </c>
       <c r="S38" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T38" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="U38" s="2">
         <v>4</v>
@@ -6421,12 +6414,12 @@
         <v>0</v>
       </c>
       <c r="AQ38" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="39" spans="1:43">
       <c r="A39" s="15" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B39" s="1">
         <v>46106</v>
@@ -6438,7 +6431,7 @@
         <v>66</v>
       </c>
       <c r="E39" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F39" s="3">
         <v>28.4</v>
@@ -6465,25 +6458,25 @@
         <v>0</v>
       </c>
       <c r="N39" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O39" t="s">
+        <v>48</v>
+      </c>
+      <c r="P39" t="s">
         <v>49</v>
       </c>
-      <c r="P39" t="s">
+      <c r="Q39" t="s">
         <v>50</v>
-      </c>
-      <c r="Q39" t="s">
-        <v>51</v>
       </c>
       <c r="R39" s="2">
         <v>67</v>
       </c>
       <c r="S39" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="T39" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="U39" s="2">
         <v>6</v>
@@ -6552,12 +6545,12 @@
         <v>0</v>
       </c>
       <c r="AQ39" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="40" spans="1:43">
       <c r="A40" s="15" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B40" s="1">
         <v>46104</v>
@@ -6569,7 +6562,7 @@
         <v>72</v>
       </c>
       <c r="E40" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F40" s="3">
         <v>24.5</v>
@@ -6596,25 +6589,25 @@
         <v>0</v>
       </c>
       <c r="N40" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O40" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="P40" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q40" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R40" s="2">
         <v>38</v>
       </c>
       <c r="S40" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="T40" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="U40" s="2">
         <v>8</v>
@@ -6683,12 +6676,12 @@
         <v>0</v>
       </c>
       <c r="AQ40" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="41" spans="1:43">
       <c r="A41" s="15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B41" s="1">
         <v>46111</v>
@@ -6700,7 +6693,7 @@
         <v>37</v>
       </c>
       <c r="E41" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F41" s="3">
         <v>26.9</v>
@@ -6727,25 +6720,25 @@
         <v>0</v>
       </c>
       <c r="N41" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="O41" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P41" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Q41" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="R41" s="2">
         <v>78</v>
       </c>
       <c r="S41" t="s">
+        <v>51</v>
+      </c>
+      <c r="T41" t="s">
         <v>52</v>
-      </c>
-      <c r="T41" t="s">
-        <v>53</v>
       </c>
       <c r="U41" s="2">
         <v>1</v>
@@ -6814,12 +6807,12 @@
         <v>0</v>
       </c>
       <c r="AQ41" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="42" spans="1:43">
       <c r="A42" s="15" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B42" s="1">
         <v>46108</v>
@@ -6831,7 +6824,7 @@
         <v>71</v>
       </c>
       <c r="E42" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F42" s="3">
         <v>35.5</v>
@@ -6858,25 +6851,25 @@
         <v>0</v>
       </c>
       <c r="N42" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="O42" t="s">
+        <v>48</v>
+      </c>
+      <c r="P42" t="s">
         <v>49</v>
       </c>
-      <c r="P42" t="s">
-        <v>50</v>
-      </c>
       <c r="Q42" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R42" s="2">
         <v>50</v>
       </c>
       <c r="S42" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="T42" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="U42" s="2">
         <v>4</v>
@@ -6945,12 +6938,12 @@
         <v>0</v>
       </c>
       <c r="AQ42" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="43" spans="1:43">
       <c r="A43" s="15" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B43" s="1">
         <v>46111</v>
@@ -6962,7 +6955,7 @@
         <v>69</v>
       </c>
       <c r="E43" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F43" s="3">
         <v>24.7</v>
@@ -6989,25 +6982,25 @@
         <v>0</v>
       </c>
       <c r="N43" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O43" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="P43" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q43" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R43" s="2">
         <v>55</v>
       </c>
       <c r="S43" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T43" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="U43" s="2">
         <v>1</v>
@@ -7076,12 +7069,12 @@
         <v>0</v>
       </c>
       <c r="AQ43" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="44" spans="1:43">
       <c r="A44" s="15" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B44" s="1">
         <v>46109</v>
@@ -7093,7 +7086,7 @@
         <v>80</v>
       </c>
       <c r="E44" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F44" s="3">
         <v>33.5</v>
@@ -7120,25 +7113,25 @@
         <v>0</v>
       </c>
       <c r="N44" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O44" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P44" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q44" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R44" s="2">
         <v>74</v>
       </c>
       <c r="S44" t="s">
+        <v>51</v>
+      </c>
+      <c r="T44" t="s">
         <v>52</v>
-      </c>
-      <c r="T44" t="s">
-        <v>53</v>
       </c>
       <c r="U44" s="2">
         <v>3</v>
@@ -7207,12 +7200,12 @@
         <v>0</v>
       </c>
       <c r="AQ44" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="45" spans="1:43">
       <c r="A45" s="15" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B45" s="1">
         <v>46108</v>
@@ -7224,7 +7217,7 @@
         <v>78</v>
       </c>
       <c r="E45" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F45" s="3">
         <v>32.4</v>
@@ -7251,25 +7244,25 @@
         <v>0</v>
       </c>
       <c r="N45" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="O45" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="P45" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Q45" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="R45" s="2">
         <v>45</v>
       </c>
       <c r="S45" t="s">
+        <v>51</v>
+      </c>
+      <c r="T45" t="s">
         <v>52</v>
-      </c>
-      <c r="T45" t="s">
-        <v>53</v>
       </c>
       <c r="U45" s="2">
         <v>4</v>
@@ -7338,12 +7331,12 @@
         <v>0</v>
       </c>
       <c r="AQ45" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="46" spans="1:43">
       <c r="A46" s="15" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B46" s="1">
         <v>46108</v>
@@ -7355,7 +7348,7 @@
         <v>75</v>
       </c>
       <c r="E46" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F46" s="3">
         <v>29.5</v>
@@ -7382,25 +7375,25 @@
         <v>0</v>
       </c>
       <c r="N46" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="O46" t="s">
+        <v>48</v>
+      </c>
+      <c r="P46" t="s">
         <v>49</v>
       </c>
-      <c r="P46" t="s">
+      <c r="Q46" t="s">
         <v>50</v>
-      </c>
-      <c r="Q46" t="s">
-        <v>51</v>
       </c>
       <c r="R46" s="2">
         <v>56</v>
       </c>
       <c r="S46" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T46" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="U46" s="2">
         <v>4</v>
@@ -7469,12 +7462,12 @@
         <v>0</v>
       </c>
       <c r="AQ46" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="47" spans="1:43">
       <c r="A47" s="15" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B47" s="1">
         <v>46105</v>
@@ -7486,7 +7479,7 @@
         <v>72</v>
       </c>
       <c r="E47" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F47" s="3">
         <v>34.700000000000003</v>
@@ -7513,25 +7506,25 @@
         <v>0</v>
       </c>
       <c r="N47" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="O47" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P47" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q47" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R47" s="2">
         <v>65</v>
       </c>
       <c r="S47" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T47" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="U47" s="2">
         <v>7</v>
@@ -7600,12 +7593,12 @@
         <v>1</v>
       </c>
       <c r="AQ47" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="48" spans="1:43">
       <c r="A48" s="15" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B48" s="1">
         <v>46108</v>
@@ -7617,7 +7610,7 @@
         <v>41</v>
       </c>
       <c r="E48" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F48" s="3">
         <v>30.3</v>
@@ -7644,25 +7637,25 @@
         <v>0</v>
       </c>
       <c r="N48" t="s">
+        <v>55</v>
+      </c>
+      <c r="O48" t="s">
         <v>56</v>
       </c>
-      <c r="O48" t="s">
-        <v>57</v>
-      </c>
       <c r="P48" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q48" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R48" s="2">
         <v>105</v>
       </c>
       <c r="S48" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T48" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="U48" s="2">
         <v>4</v>
@@ -7731,12 +7724,12 @@
         <v>1</v>
       </c>
       <c r="AQ48" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="49" spans="1:43">
       <c r="A49" s="15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B49" s="1">
         <v>46110</v>
@@ -7748,7 +7741,7 @@
         <v>29</v>
       </c>
       <c r="E49" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F49" s="3">
         <v>22.9</v>
@@ -7775,25 +7768,25 @@
         <v>0</v>
       </c>
       <c r="N49" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O49" t="s">
+        <v>48</v>
+      </c>
+      <c r="P49" t="s">
         <v>49</v>
       </c>
-      <c r="P49" t="s">
-        <v>50</v>
-      </c>
       <c r="Q49" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R49" s="2">
         <v>32</v>
       </c>
       <c r="S49" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T49" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="U49" s="2">
         <v>2</v>
@@ -7862,12 +7855,12 @@
         <v>1</v>
       </c>
       <c r="AQ49" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="50" spans="1:43">
       <c r="A50" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B50" s="1">
         <v>46107</v>
@@ -7879,7 +7872,7 @@
         <v>82</v>
       </c>
       <c r="E50" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F50" s="3">
         <v>26.8</v>
@@ -7906,25 +7899,25 @@
         <v>0</v>
       </c>
       <c r="N50" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O50" t="s">
+        <v>48</v>
+      </c>
+      <c r="P50" t="s">
         <v>49</v>
       </c>
-      <c r="P50" t="s">
-        <v>50</v>
-      </c>
       <c r="Q50" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R50" s="2">
         <v>29</v>
       </c>
       <c r="S50" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="T50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="U50" s="2">
         <v>5</v>
@@ -7993,12 +7986,12 @@
         <v>1</v>
       </c>
       <c r="AQ50" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="51" spans="1:43">
       <c r="A51" s="15" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B51" s="1">
         <v>46108</v>
@@ -8010,7 +8003,7 @@
         <v>57</v>
       </c>
       <c r="E51" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F51" s="3">
         <v>26.8</v>
@@ -8037,25 +8030,25 @@
         <v>0</v>
       </c>
       <c r="N51" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O51" t="s">
+        <v>48</v>
+      </c>
+      <c r="P51" t="s">
         <v>49</v>
       </c>
-      <c r="P51" t="s">
+      <c r="Q51" t="s">
         <v>50</v>
-      </c>
-      <c r="Q51" t="s">
-        <v>51</v>
       </c>
       <c r="R51" s="2">
         <v>65</v>
       </c>
       <c r="S51" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="T51" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="U51" s="2">
         <v>4</v>
@@ -8124,12 +8117,12 @@
         <v>1</v>
       </c>
       <c r="AQ51" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="52" spans="1:43">
       <c r="A52" s="15" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B52" s="1">
         <v>46106</v>
@@ -8141,7 +8134,7 @@
         <v>34</v>
       </c>
       <c r="E52" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F52" s="3">
         <v>29.4</v>
@@ -8168,25 +8161,25 @@
         <v>0</v>
       </c>
       <c r="N52" t="s">
+        <v>55</v>
+      </c>
+      <c r="O52" t="s">
         <v>56</v>
       </c>
-      <c r="O52" t="s">
+      <c r="P52" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q52" t="s">
         <v>57</v>
-      </c>
-      <c r="P52" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q52" t="s">
-        <v>58</v>
       </c>
       <c r="R52" s="2">
         <v>38</v>
       </c>
       <c r="S52" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T52" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="U52" s="2">
         <v>6</v>
@@ -8255,12 +8248,12 @@
         <v>1</v>
       </c>
       <c r="AQ52" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="53" spans="1:43">
       <c r="A53" s="15" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B53" s="1">
         <v>46110</v>
@@ -8272,7 +8265,7 @@
         <v>49</v>
       </c>
       <c r="E53" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F53" s="3">
         <v>26.1</v>
@@ -8299,25 +8292,25 @@
         <v>0</v>
       </c>
       <c r="N53" t="s">
+        <v>55</v>
+      </c>
+      <c r="O53" t="s">
         <v>56</v>
       </c>
-      <c r="O53" t="s">
-        <v>57</v>
-      </c>
       <c r="P53" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q53" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R53" s="2">
         <v>37</v>
       </c>
       <c r="S53" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T53" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="U53" s="2">
         <v>2</v>
@@ -8386,12 +8379,12 @@
         <v>1</v>
       </c>
       <c r="AQ53" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="54" spans="1:43">
       <c r="A54" s="15" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B54" s="1">
         <v>46108</v>
@@ -8403,7 +8396,7 @@
         <v>66</v>
       </c>
       <c r="E54" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F54" s="3">
         <v>27.4</v>
@@ -8430,25 +8423,25 @@
         <v>0</v>
       </c>
       <c r="N54" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O54" t="s">
+        <v>48</v>
+      </c>
+      <c r="P54" t="s">
         <v>49</v>
       </c>
-      <c r="P54" t="s">
+      <c r="Q54" t="s">
         <v>50</v>
-      </c>
-      <c r="Q54" t="s">
-        <v>51</v>
       </c>
       <c r="R54" s="2">
         <v>36</v>
       </c>
       <c r="S54" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T54" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="U54" s="2">
         <v>4</v>
@@ -8517,12 +8510,12 @@
         <v>1</v>
       </c>
       <c r="AQ54" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="55" spans="1:43">
       <c r="A55" s="15" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B55" s="1">
         <v>46107</v>
@@ -8534,7 +8527,7 @@
         <v>63</v>
       </c>
       <c r="E55" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F55" s="3">
         <v>33.1</v>
@@ -8561,25 +8554,25 @@
         <v>0</v>
       </c>
       <c r="N55" t="s">
+        <v>55</v>
+      </c>
+      <c r="O55" t="s">
         <v>56</v>
       </c>
-      <c r="O55" t="s">
-        <v>57</v>
-      </c>
       <c r="P55" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q55" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R55" s="2">
         <v>44</v>
       </c>
       <c r="S55" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T55" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="U55" s="2">
         <v>5</v>
@@ -8648,12 +8641,12 @@
         <v>1</v>
       </c>
       <c r="AQ55" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="56" spans="1:43">
       <c r="A56" s="15" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B56" s="1">
         <v>46106</v>
@@ -8665,7 +8658,7 @@
         <v>61</v>
       </c>
       <c r="E56" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F56" s="3">
         <v>22.1</v>
@@ -8692,25 +8685,25 @@
         <v>0</v>
       </c>
       <c r="N56" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O56" t="s">
+        <v>56</v>
+      </c>
+      <c r="P56" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q56" t="s">
         <v>57</v>
-      </c>
-      <c r="P56" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q56" t="s">
-        <v>58</v>
       </c>
       <c r="R56" s="2">
         <v>49</v>
       </c>
       <c r="S56" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="T56" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="U56" s="2">
         <v>6</v>
@@ -8779,12 +8772,12 @@
         <v>1</v>
       </c>
       <c r="AQ56" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="57" spans="1:43">
       <c r="A57" s="15" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B57" s="1">
         <v>46111</v>
@@ -8796,7 +8789,7 @@
         <v>64</v>
       </c>
       <c r="E57" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F57" s="3">
         <v>32</v>
@@ -8823,25 +8816,25 @@
         <v>0</v>
       </c>
       <c r="N57" t="s">
+        <v>47</v>
+      </c>
+      <c r="O57" t="s">
         <v>48</v>
       </c>
-      <c r="O57" t="s">
+      <c r="P57" t="s">
         <v>49</v>
       </c>
-      <c r="P57" t="s">
-        <v>50</v>
-      </c>
       <c r="Q57" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R57" s="2">
         <v>57</v>
       </c>
       <c r="S57" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="T57" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="U57" s="2">
         <v>1</v>
@@ -8910,12 +8903,12 @@
         <v>1</v>
       </c>
       <c r="AQ57" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="58" spans="1:43">
       <c r="A58" s="15" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B58" s="1">
         <v>46106</v>
@@ -8927,7 +8920,7 @@
         <v>66</v>
       </c>
       <c r="E58" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F58" s="3">
         <v>28.4</v>
@@ -8954,25 +8947,25 @@
         <v>0</v>
       </c>
       <c r="N58" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O58" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="P58" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q58" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R58" s="2">
         <v>43</v>
       </c>
       <c r="S58" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T58" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="U58" s="2">
         <v>6</v>
@@ -9041,12 +9034,12 @@
         <v>1</v>
       </c>
       <c r="AQ58" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="59" spans="1:43">
       <c r="A59" s="15" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B59" s="1">
         <v>46109</v>
@@ -9058,7 +9051,7 @@
         <v>38</v>
       </c>
       <c r="E59" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F59" s="3">
         <v>26.3</v>
@@ -9085,25 +9078,25 @@
         <v>0</v>
       </c>
       <c r="N59" t="s">
+        <v>47</v>
+      </c>
+      <c r="O59" t="s">
         <v>48</v>
       </c>
-      <c r="O59" t="s">
+      <c r="P59" t="s">
         <v>49</v>
       </c>
-      <c r="P59" t="s">
-        <v>50</v>
-      </c>
       <c r="Q59" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R59" s="2">
         <v>55</v>
       </c>
       <c r="S59" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="T59" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="U59" s="2">
         <v>3</v>
@@ -9172,12 +9165,12 @@
         <v>1</v>
       </c>
       <c r="AQ59" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="60" spans="1:43">
       <c r="A60" s="15" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B60" s="1">
         <v>46110</v>
@@ -9189,7 +9182,7 @@
         <v>36</v>
       </c>
       <c r="E60" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F60" s="3">
         <v>29.6</v>
@@ -9216,25 +9209,25 @@
         <v>0</v>
       </c>
       <c r="N60" t="s">
+        <v>55</v>
+      </c>
+      <c r="O60" t="s">
         <v>56</v>
       </c>
-      <c r="O60" t="s">
-        <v>57</v>
-      </c>
       <c r="P60" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q60" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R60" s="2">
         <v>87</v>
       </c>
       <c r="S60" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T60" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="U60" s="2">
         <v>2</v>
@@ -9303,12 +9296,12 @@
         <v>1</v>
       </c>
       <c r="AQ60" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="61" spans="1:43">
       <c r="A61" s="15" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B61" s="1">
         <v>46106</v>
@@ -9320,7 +9313,7 @@
         <v>82</v>
       </c>
       <c r="E61" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F61" s="3">
         <v>32.4</v>
@@ -9347,25 +9340,25 @@
         <v>0</v>
       </c>
       <c r="N61" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="O61" t="s">
+        <v>48</v>
+      </c>
+      <c r="P61" t="s">
         <v>49</v>
       </c>
-      <c r="P61" t="s">
+      <c r="Q61" t="s">
         <v>50</v>
-      </c>
-      <c r="Q61" t="s">
-        <v>51</v>
       </c>
       <c r="R61" s="2">
         <v>85</v>
       </c>
       <c r="S61" t="s">
+        <v>51</v>
+      </c>
+      <c r="T61" t="s">
         <v>52</v>
-      </c>
-      <c r="T61" t="s">
-        <v>53</v>
       </c>
       <c r="U61" s="2">
         <v>6</v>
@@ -9434,12 +9427,12 @@
         <v>1</v>
       </c>
       <c r="AQ61" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="62" spans="1:43">
       <c r="A62" s="15" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B62" s="1">
         <v>46106</v>
@@ -9451,7 +9444,7 @@
         <v>62</v>
       </c>
       <c r="E62" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F62" s="3">
         <v>24.5</v>
@@ -9478,25 +9471,25 @@
         <v>0</v>
       </c>
       <c r="N62" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O62" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="P62" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q62" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R62" s="2">
         <v>36</v>
       </c>
       <c r="S62" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="T62" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="U62" s="2">
         <v>6</v>
@@ -9565,12 +9558,12 @@
         <v>1</v>
       </c>
       <c r="AQ62" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="63" spans="1:43">
       <c r="A63" s="15" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B63" s="1">
         <v>46110</v>
@@ -9582,7 +9575,7 @@
         <v>35</v>
       </c>
       <c r="E63" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F63" s="3">
         <v>25.1</v>
@@ -9609,25 +9602,25 @@
         <v>0</v>
       </c>
       <c r="N63" t="s">
+        <v>47</v>
+      </c>
+      <c r="O63" t="s">
         <v>48</v>
       </c>
-      <c r="O63" t="s">
+      <c r="P63" t="s">
         <v>49</v>
       </c>
-      <c r="P63" t="s">
-        <v>50</v>
-      </c>
       <c r="Q63" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R63" s="2">
         <v>25</v>
       </c>
       <c r="S63" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T63" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="U63" s="2">
         <v>2</v>
@@ -9696,12 +9689,12 @@
         <v>1</v>
       </c>
       <c r="AQ63" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="64" spans="1:43">
       <c r="A64" s="15" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B64" s="1">
         <v>46111</v>
@@ -9713,7 +9706,7 @@
         <v>46</v>
       </c>
       <c r="E64" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F64" s="3">
         <v>34.299999999999997</v>
@@ -9740,25 +9733,25 @@
         <v>0</v>
       </c>
       <c r="N64" t="s">
+        <v>47</v>
+      </c>
+      <c r="O64" t="s">
         <v>48</v>
       </c>
-      <c r="O64" t="s">
+      <c r="P64" t="s">
         <v>49</v>
       </c>
-      <c r="P64" t="s">
-        <v>50</v>
-      </c>
       <c r="Q64" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="R64" s="2">
         <v>51</v>
       </c>
       <c r="S64" t="s">
+        <v>51</v>
+      </c>
+      <c r="T64" t="s">
         <v>52</v>
-      </c>
-      <c r="T64" t="s">
-        <v>53</v>
       </c>
       <c r="U64" s="2">
         <v>1</v>
@@ -9827,12 +9820,12 @@
         <v>1</v>
       </c>
       <c r="AQ64" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="65" spans="1:43">
       <c r="A65" s="15" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B65" s="1">
         <v>46106</v>
@@ -9844,7 +9837,7 @@
         <v>29</v>
       </c>
       <c r="E65" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F65" s="3">
         <v>30.2</v>
@@ -9871,25 +9864,25 @@
         <v>0</v>
       </c>
       <c r="N65" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O65" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="P65" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q65" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R65" s="2">
         <v>23</v>
       </c>
       <c r="S65" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="T65" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="U65" s="2">
         <v>6</v>
@@ -9958,12 +9951,12 @@
         <v>1</v>
       </c>
       <c r="AQ65" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="66" spans="1:43">
       <c r="A66" s="15" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B66" s="1">
         <v>46109</v>
@@ -9975,7 +9968,7 @@
         <v>75</v>
       </c>
       <c r="E66" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F66" s="3">
         <v>21.2</v>
@@ -10002,25 +9995,25 @@
         <v>0</v>
       </c>
       <c r="N66" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O66" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="P66" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q66" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R66" s="2">
         <v>42</v>
       </c>
       <c r="S66" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="T66" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="U66" s="2">
         <v>3</v>
@@ -10089,12 +10082,12 @@
         <v>1</v>
       </c>
       <c r="AQ66" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="67" spans="1:43">
       <c r="A67" s="15" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B67" s="1">
         <v>46104</v>
@@ -10106,7 +10099,7 @@
         <v>40</v>
       </c>
       <c r="E67" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F67" s="3">
         <v>33.799999999999997</v>
@@ -10133,25 +10126,25 @@
         <v>1</v>
       </c>
       <c r="N67" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="O67" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="P67" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Q67" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R67" s="2">
         <v>56</v>
       </c>
       <c r="S67" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="T67" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="U67" s="2">
         <v>8</v>
@@ -10220,12 +10213,12 @@
         <v>1</v>
       </c>
       <c r="AQ67" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="68" spans="1:43">
       <c r="A68" s="15" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B68" s="1">
         <v>46109</v>
@@ -10237,7 +10230,7 @@
         <v>59</v>
       </c>
       <c r="E68" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F68" s="3">
         <v>26.3</v>
@@ -10264,25 +10257,25 @@
         <v>0</v>
       </c>
       <c r="N68" t="s">
+        <v>47</v>
+      </c>
+      <c r="O68" t="s">
         <v>48</v>
       </c>
-      <c r="O68" t="s">
+      <c r="P68" t="s">
         <v>49</v>
       </c>
-      <c r="P68" t="s">
-        <v>50</v>
-      </c>
       <c r="Q68" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R68" s="2">
         <v>36</v>
       </c>
       <c r="S68" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T68" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="U68" s="2">
         <v>3</v>
@@ -10351,12 +10344,12 @@
         <v>1</v>
       </c>
       <c r="AQ68" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="69" spans="1:43">
       <c r="A69" s="15" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B69" s="1">
         <v>46108</v>
@@ -10368,7 +10361,7 @@
         <v>78</v>
       </c>
       <c r="E69" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F69" s="3">
         <v>34.700000000000003</v>
@@ -10395,25 +10388,25 @@
         <v>0</v>
       </c>
       <c r="N69" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="O69" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="P69" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q69" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R69" s="2">
         <v>41</v>
       </c>
       <c r="S69" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T69" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="U69" s="2">
         <v>4</v>
@@ -10482,12 +10475,12 @@
         <v>1</v>
       </c>
       <c r="AQ69" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="70" spans="1:43">
       <c r="A70" s="15" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B70" s="1">
         <v>46109</v>
@@ -10499,7 +10492,7 @@
         <v>64</v>
       </c>
       <c r="E70" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F70" s="3">
         <v>23</v>
@@ -10526,25 +10519,25 @@
         <v>0</v>
       </c>
       <c r="N70" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="O70" t="s">
+        <v>48</v>
+      </c>
+      <c r="P70" t="s">
         <v>49</v>
       </c>
-      <c r="P70" t="s">
+      <c r="Q70" t="s">
         <v>50</v>
-      </c>
-      <c r="Q70" t="s">
-        <v>51</v>
       </c>
       <c r="R70" s="2">
         <v>52</v>
       </c>
       <c r="S70" t="s">
+        <v>51</v>
+      </c>
+      <c r="T70" t="s">
         <v>52</v>
-      </c>
-      <c r="T70" t="s">
-        <v>53</v>
       </c>
       <c r="U70" s="2">
         <v>3</v>
@@ -10613,12 +10606,12 @@
         <v>1</v>
       </c>
       <c r="AQ70" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="71" spans="1:43">
       <c r="A71" s="15" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B71" s="1">
         <v>46110</v>
@@ -10630,7 +10623,7 @@
         <v>33</v>
       </c>
       <c r="E71" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F71" s="3">
         <v>32.799999999999997</v>
@@ -10657,25 +10650,25 @@
         <v>0</v>
       </c>
       <c r="N71" t="s">
+        <v>47</v>
+      </c>
+      <c r="O71" t="s">
         <v>48</v>
       </c>
-      <c r="O71" t="s">
+      <c r="P71" t="s">
         <v>49</v>
       </c>
-      <c r="P71" t="s">
+      <c r="Q71" t="s">
         <v>50</v>
-      </c>
-      <c r="Q71" t="s">
-        <v>51</v>
       </c>
       <c r="R71" s="2">
         <v>49</v>
       </c>
       <c r="S71" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T71" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="U71" s="2">
         <v>2</v>
@@ -10744,12 +10737,12 @@
         <v>1</v>
       </c>
       <c r="AQ71" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="72" spans="1:43">
       <c r="A72" s="15" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B72" s="1">
         <v>46110</v>
@@ -10761,7 +10754,7 @@
         <v>64</v>
       </c>
       <c r="E72" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F72" s="3">
         <v>26.3</v>
@@ -10788,25 +10781,25 @@
         <v>0</v>
       </c>
       <c r="N72" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="O72" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="P72" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Q72" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R72" s="2">
         <v>48</v>
       </c>
       <c r="S72" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T72" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="U72" s="2">
         <v>2</v>
@@ -10875,12 +10868,12 @@
         <v>1</v>
       </c>
       <c r="AQ72" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="73" spans="1:43">
       <c r="A73" s="15" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B73" s="1">
         <v>46107</v>
@@ -10892,7 +10885,7 @@
         <v>31</v>
       </c>
       <c r="E73" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F73" s="3">
         <v>33.1</v>
@@ -10919,25 +10912,25 @@
         <v>0</v>
       </c>
       <c r="N73" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="O73" t="s">
+        <v>48</v>
+      </c>
+      <c r="P73" t="s">
         <v>49</v>
       </c>
-      <c r="P73" t="s">
-        <v>50</v>
-      </c>
       <c r="Q73" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R73" s="2">
         <v>35</v>
       </c>
       <c r="S73" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="T73" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="U73" s="2">
         <v>5</v>
@@ -11006,12 +10999,12 @@
         <v>1</v>
       </c>
       <c r="AQ73" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="74" spans="1:43">
       <c r="A74" s="15" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B74" s="1">
         <v>46107</v>
@@ -11023,7 +11016,7 @@
         <v>37</v>
       </c>
       <c r="E74" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F74" s="3">
         <v>23.5</v>
@@ -11050,25 +11043,25 @@
         <v>0</v>
       </c>
       <c r="N74" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O74" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P74" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q74" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R74" s="2">
         <v>68</v>
       </c>
       <c r="S74" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T74" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="U74" s="2">
         <v>5</v>
@@ -11137,12 +11130,12 @@
         <v>1</v>
       </c>
       <c r="AQ74" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="75" spans="1:43">
       <c r="A75" s="15" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B75" s="1">
         <v>46107</v>
@@ -11154,7 +11147,7 @@
         <v>58</v>
       </c>
       <c r="E75" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F75" s="3">
         <v>24.6</v>
@@ -11181,25 +11174,25 @@
         <v>0</v>
       </c>
       <c r="N75" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="O75" t="s">
+        <v>48</v>
+      </c>
+      <c r="P75" t="s">
         <v>49</v>
       </c>
-      <c r="P75" t="s">
-        <v>50</v>
-      </c>
       <c r="Q75" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="R75" s="2">
         <v>61</v>
       </c>
       <c r="S75" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T75" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="U75" s="2">
         <v>5</v>
@@ -11268,12 +11261,12 @@
         <v>1</v>
       </c>
       <c r="AQ75" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="76" spans="1:43">
       <c r="A76" s="15" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B76" s="1">
         <v>46112</v>
@@ -11285,7 +11278,7 @@
         <v>67</v>
       </c>
       <c r="E76" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F76" s="3">
         <v>24.9</v>
@@ -11312,25 +11305,25 @@
         <v>0</v>
       </c>
       <c r="N76" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O76" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P76" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q76" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R76" s="2">
         <v>78</v>
       </c>
       <c r="S76" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="T76" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="U76" s="2">
         <v>0</v>
@@ -11399,12 +11392,12 @@
         <v>1</v>
       </c>
       <c r="AQ76" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="77" spans="1:43">
       <c r="A77" s="15" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B77" s="1">
         <v>46112</v>
@@ -11416,7 +11409,7 @@
         <v>72</v>
       </c>
       <c r="E77" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F77" s="3">
         <v>33.799999999999997</v>
@@ -11443,25 +11436,25 @@
         <v>0</v>
       </c>
       <c r="N77" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O77" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P77" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q77" t="s">
         <v>50</v>
-      </c>
-      <c r="Q77" t="s">
-        <v>51</v>
       </c>
       <c r="R77" s="2">
         <v>67</v>
       </c>
       <c r="S77" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="T77" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="U77" s="2">
         <v>0</v>
@@ -11530,12 +11523,12 @@
         <v>1</v>
       </c>
       <c r="AQ77" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="78" spans="1:43">
       <c r="A78" s="15" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B78" s="1">
         <v>46109</v>
@@ -11547,7 +11540,7 @@
         <v>75</v>
       </c>
       <c r="E78" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F78" s="3">
         <v>23.1</v>
@@ -11574,25 +11567,25 @@
         <v>0</v>
       </c>
       <c r="N78" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O78" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P78" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q78" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="R78" s="2">
         <v>71</v>
       </c>
       <c r="S78" t="s">
+        <v>51</v>
+      </c>
+      <c r="T78" t="s">
         <v>52</v>
-      </c>
-      <c r="T78" t="s">
-        <v>53</v>
       </c>
       <c r="U78" s="2">
         <v>3</v>
@@ -11661,12 +11654,12 @@
         <v>1</v>
       </c>
       <c r="AQ78" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="79" spans="1:43">
       <c r="A79" s="15" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B79" s="1">
         <v>46102</v>
@@ -11678,7 +11671,7 @@
         <v>65</v>
       </c>
       <c r="E79" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F79" s="3">
         <v>25.5</v>
@@ -11705,25 +11698,25 @@
         <v>0</v>
       </c>
       <c r="N79" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O79" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="P79" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q79" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R79" s="2">
         <v>29</v>
       </c>
       <c r="S79" t="s">
+        <v>67</v>
+      </c>
+      <c r="T79" t="s">
         <v>68</v>
-      </c>
-      <c r="T79" t="s">
-        <v>69</v>
       </c>
       <c r="U79" s="2">
         <v>10</v>
@@ -11792,12 +11785,12 @@
         <v>1</v>
       </c>
       <c r="AQ79" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="80" spans="1:43">
       <c r="A80" s="15" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B80" s="1">
         <v>46102</v>
@@ -11809,7 +11802,7 @@
         <v>40</v>
       </c>
       <c r="E80" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F80" s="3">
         <v>21.3</v>
@@ -11836,25 +11829,25 @@
         <v>0</v>
       </c>
       <c r="N80" t="s">
+        <v>55</v>
+      </c>
+      <c r="O80" t="s">
         <v>56</v>
       </c>
-      <c r="O80" t="s">
-        <v>57</v>
-      </c>
       <c r="P80" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q80" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R80" s="2">
         <v>52</v>
       </c>
       <c r="S80" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="T80" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="U80" s="2">
         <v>10</v>
@@ -11923,12 +11916,12 @@
         <v>1</v>
       </c>
       <c r="AQ80" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="81" spans="1:43">
       <c r="A81" s="15" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B81" s="1">
         <v>46100</v>
@@ -11940,7 +11933,7 @@
         <v>77</v>
       </c>
       <c r="E81" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F81" s="3">
         <v>33.6</v>
@@ -11967,25 +11960,25 @@
         <v>0</v>
       </c>
       <c r="N81" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="O81" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P81" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q81" t="s">
         <v>50</v>
-      </c>
-      <c r="Q81" t="s">
-        <v>51</v>
       </c>
       <c r="R81" s="2">
         <v>68</v>
       </c>
       <c r="S81" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T81" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="U81" s="2">
         <v>12</v>
@@ -12054,12 +12047,12 @@
         <v>1</v>
       </c>
       <c r="AQ81" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="82" spans="1:43">
       <c r="A82" s="15" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B82" s="1">
         <v>46112</v>
@@ -12071,7 +12064,7 @@
         <v>84</v>
       </c>
       <c r="E82" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F82" s="3">
         <v>32.9</v>
@@ -12098,25 +12091,25 @@
         <v>0</v>
       </c>
       <c r="N82" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O82" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P82" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q82" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="R82" s="2">
         <v>76</v>
       </c>
       <c r="S82" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="T82" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="U82" s="2">
         <v>0</v>
@@ -12185,12 +12178,12 @@
         <v>2</v>
       </c>
       <c r="AQ82" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="83" spans="1:43">
       <c r="A83" s="15" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B83" s="1">
         <v>46109</v>
@@ -12202,7 +12195,7 @@
         <v>68</v>
       </c>
       <c r="E83" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F83" s="3">
         <v>27.9</v>
@@ -12229,25 +12222,25 @@
         <v>0</v>
       </c>
       <c r="N83" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="O83" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P83" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Q83" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="R83" s="2">
         <v>81</v>
       </c>
       <c r="S83" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T83" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="U83" s="2">
         <v>3</v>
@@ -12316,12 +12309,12 @@
         <v>2</v>
       </c>
       <c r="AQ83" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="84" spans="1:43">
       <c r="A84" s="15" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B84" s="1">
         <v>46109</v>
@@ -12333,7 +12326,7 @@
         <v>79</v>
       </c>
       <c r="E84" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F84" s="3">
         <v>28.6</v>
@@ -12360,25 +12353,25 @@
         <v>0</v>
       </c>
       <c r="N84" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="O84" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="P84" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q84" t="s">
         <v>50</v>
-      </c>
-      <c r="Q84" t="s">
-        <v>51</v>
       </c>
       <c r="R84" s="2">
         <v>47</v>
       </c>
       <c r="S84" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="T84" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="U84" s="2">
         <v>3</v>
@@ -12447,12 +12440,12 @@
         <v>2</v>
       </c>
       <c r="AQ84" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="85" spans="1:43">
       <c r="A85" s="15" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B85" s="1">
         <v>46111</v>
@@ -12464,7 +12457,7 @@
         <v>70</v>
       </c>
       <c r="E85" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F85" s="3">
         <v>34.799999999999997</v>
@@ -12491,25 +12484,25 @@
         <v>0</v>
       </c>
       <c r="N85" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O85" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P85" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q85" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R85" s="2">
         <v>59</v>
       </c>
       <c r="S85" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T85" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="U85" s="2">
         <v>1</v>
@@ -12578,12 +12571,12 @@
         <v>2</v>
       </c>
       <c r="AQ85" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="86" spans="1:43">
       <c r="A86" s="15" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B86" s="1">
         <v>46111</v>
@@ -12595,7 +12588,7 @@
         <v>85</v>
       </c>
       <c r="E86" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F86" s="3">
         <v>30.6</v>
@@ -12622,25 +12615,25 @@
         <v>0</v>
       </c>
       <c r="N86" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O86" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="P86" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q86" t="s">
         <v>50</v>
-      </c>
-      <c r="Q86" t="s">
-        <v>51</v>
       </c>
       <c r="R86" s="2">
         <v>75</v>
       </c>
       <c r="S86" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="T86" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="U86" s="2">
         <v>1</v>
@@ -12709,12 +12702,12 @@
         <v>2</v>
       </c>
       <c r="AQ86" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="87" spans="1:43">
       <c r="A87" s="15" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B87" s="1">
         <v>46109</v>
@@ -12726,7 +12719,7 @@
         <v>74</v>
       </c>
       <c r="E87" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F87" s="3">
         <v>27.7</v>
@@ -12753,25 +12746,25 @@
         <v>1</v>
       </c>
       <c r="N87" t="s">
+        <v>47</v>
+      </c>
+      <c r="O87" t="s">
         <v>48</v>
       </c>
-      <c r="O87" t="s">
-        <v>49</v>
-      </c>
       <c r="P87" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Q87" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="R87" s="2">
         <v>41</v>
       </c>
       <c r="S87" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T87" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="U87" s="2">
         <v>3</v>
@@ -12840,12 +12833,12 @@
         <v>2</v>
       </c>
       <c r="AQ87" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="88" spans="1:43">
       <c r="A88" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B88" s="1">
         <v>46112</v>
@@ -12857,7 +12850,7 @@
         <v>84</v>
       </c>
       <c r="E88" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F88" s="3">
         <v>22.7</v>
@@ -12884,25 +12877,25 @@
         <v>0</v>
       </c>
       <c r="N88" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="O88" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="P88" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q88" t="s">
         <v>50</v>
-      </c>
-      <c r="Q88" t="s">
-        <v>51</v>
       </c>
       <c r="R88" s="2">
         <v>53</v>
       </c>
       <c r="S88" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="T88" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="U88" s="2">
         <v>0</v>
@@ -12971,12 +12964,12 @@
         <v>2</v>
       </c>
       <c r="AQ88" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="89" spans="1:43">
       <c r="A89" s="15" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B89" s="1">
         <v>46111</v>
@@ -12988,7 +12981,7 @@
         <v>76</v>
       </c>
       <c r="E89" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F89" s="3">
         <v>33.6</v>
@@ -13015,25 +13008,25 @@
         <v>0</v>
       </c>
       <c r="N89" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O89" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P89" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Q89" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="R89" s="2">
         <v>81</v>
       </c>
       <c r="S89" t="s">
+        <v>51</v>
+      </c>
+      <c r="T89" t="s">
         <v>52</v>
-      </c>
-      <c r="T89" t="s">
-        <v>53</v>
       </c>
       <c r="U89" s="2">
         <v>1</v>
@@ -13102,12 +13095,12 @@
         <v>2</v>
       </c>
       <c r="AQ89" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="90" spans="1:43">
       <c r="A90" s="15" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B90" s="1">
         <v>46103</v>
@@ -13119,7 +13112,7 @@
         <v>69</v>
       </c>
       <c r="E90" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F90" s="3">
         <v>33.9</v>
@@ -13146,25 +13139,25 @@
         <v>0</v>
       </c>
       <c r="N90" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="O90" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P90" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q90" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="R90" s="2">
         <v>72</v>
       </c>
       <c r="S90" t="s">
+        <v>51</v>
+      </c>
+      <c r="T90" t="s">
         <v>52</v>
-      </c>
-      <c r="T90" t="s">
-        <v>53</v>
       </c>
       <c r="U90" s="2">
         <v>9</v>
@@ -13233,12 +13226,12 @@
         <v>2</v>
       </c>
       <c r="AQ90" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="91" spans="1:43">
       <c r="A91" s="15" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B91" s="1">
         <v>46106</v>
@@ -13250,7 +13243,7 @@
         <v>45</v>
       </c>
       <c r="E91" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F91" s="3">
         <v>32.1</v>
@@ -13277,25 +13270,25 @@
         <v>0</v>
       </c>
       <c r="N91" t="s">
+        <v>47</v>
+      </c>
+      <c r="O91" t="s">
         <v>48</v>
       </c>
-      <c r="O91" t="s">
-        <v>49</v>
-      </c>
       <c r="P91" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Q91" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="R91" s="2">
         <v>49</v>
       </c>
       <c r="S91" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="T91" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="U91" s="2">
         <v>6</v>
@@ -13364,12 +13357,12 @@
         <v>2</v>
       </c>
       <c r="AQ91" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="92" spans="1:43">
       <c r="A92" s="15" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B92" s="1">
         <v>46105</v>
@@ -13381,7 +13374,7 @@
         <v>44</v>
       </c>
       <c r="E92" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F92" s="3">
         <v>29.4</v>
@@ -13408,25 +13401,25 @@
         <v>0</v>
       </c>
       <c r="N92" t="s">
+        <v>47</v>
+      </c>
+      <c r="O92" t="s">
         <v>48</v>
       </c>
-      <c r="O92" t="s">
+      <c r="P92" t="s">
         <v>49</v>
       </c>
-      <c r="P92" t="s">
-        <v>50</v>
-      </c>
       <c r="Q92" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R92" s="2">
         <v>32</v>
       </c>
       <c r="S92" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="T92" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="U92" s="2">
         <v>7</v>
@@ -13495,12 +13488,12 @@
         <v>2</v>
       </c>
       <c r="AQ92" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="93" spans="1:43">
       <c r="A93" s="15" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B93" s="1">
         <v>46107</v>
@@ -13512,7 +13505,7 @@
         <v>74</v>
       </c>
       <c r="E93" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F93" s="3">
         <v>32.9</v>
@@ -13539,25 +13532,25 @@
         <v>0</v>
       </c>
       <c r="N93" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="O93" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="P93" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q93" t="s">
         <v>50</v>
-      </c>
-      <c r="Q93" t="s">
-        <v>51</v>
       </c>
       <c r="R93" s="2">
         <v>34</v>
       </c>
       <c r="S93" t="s">
+        <v>51</v>
+      </c>
+      <c r="T93" t="s">
         <v>52</v>
-      </c>
-      <c r="T93" t="s">
-        <v>53</v>
       </c>
       <c r="U93" s="2">
         <v>5</v>
@@ -13626,12 +13619,12 @@
         <v>2</v>
       </c>
       <c r="AQ93" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="94" spans="1:43">
       <c r="A94" s="15" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B94" s="1">
         <v>46106</v>
@@ -13643,7 +13636,7 @@
         <v>67</v>
       </c>
       <c r="E94" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F94" s="3">
         <v>29.3</v>
@@ -13670,25 +13663,25 @@
         <v>0</v>
       </c>
       <c r="N94" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O94" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="P94" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q94" t="s">
         <v>50</v>
-      </c>
-      <c r="Q94" t="s">
-        <v>51</v>
       </c>
       <c r="R94" s="2">
         <v>49</v>
       </c>
       <c r="S94" t="s">
+        <v>51</v>
+      </c>
+      <c r="T94" t="s">
         <v>52</v>
-      </c>
-      <c r="T94" t="s">
-        <v>53</v>
       </c>
       <c r="U94" s="2">
         <v>6</v>
@@ -13757,12 +13750,12 @@
         <v>2</v>
       </c>
       <c r="AQ94" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="95" spans="1:43">
       <c r="A95" s="15" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B95" s="1">
         <v>46109</v>
@@ -13774,7 +13767,7 @@
         <v>47</v>
       </c>
       <c r="E95" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F95" s="3">
         <v>35.799999999999997</v>
@@ -13801,25 +13794,25 @@
         <v>0</v>
       </c>
       <c r="N95" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="O95" t="s">
+        <v>48</v>
+      </c>
+      <c r="P95" t="s">
         <v>49</v>
       </c>
-      <c r="P95" t="s">
+      <c r="Q95" t="s">
         <v>50</v>
-      </c>
-      <c r="Q95" t="s">
-        <v>51</v>
       </c>
       <c r="R95" s="2">
         <v>41</v>
       </c>
       <c r="S95" t="s">
+        <v>51</v>
+      </c>
+      <c r="T95" t="s">
         <v>52</v>
-      </c>
-      <c r="T95" t="s">
-        <v>53</v>
       </c>
       <c r="U95" s="2">
         <v>3</v>
@@ -13888,12 +13881,12 @@
         <v>2</v>
       </c>
       <c r="AQ95" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="96" spans="1:43">
       <c r="A96" s="15" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B96" s="1">
         <v>46110</v>
@@ -13905,7 +13898,7 @@
         <v>41</v>
       </c>
       <c r="E96" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F96" s="3">
         <v>29.5</v>
@@ -13932,25 +13925,25 @@
         <v>1</v>
       </c>
       <c r="N96" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O96" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="P96" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Q96" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R96" s="2">
         <v>50</v>
       </c>
       <c r="S96" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="T96" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="U96" s="2">
         <v>2</v>
@@ -14019,12 +14012,12 @@
         <v>2</v>
       </c>
       <c r="AQ96" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="97" spans="1:43">
       <c r="A97" s="15" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B97" s="1">
         <v>46109</v>
@@ -14036,7 +14029,7 @@
         <v>66</v>
       </c>
       <c r="E97" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F97" s="3">
         <v>26.8</v>
@@ -14063,25 +14056,25 @@
         <v>1</v>
       </c>
       <c r="N97" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="O97" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="P97" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q97" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R97" s="2">
         <v>30</v>
       </c>
       <c r="S97" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="T97" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="U97" s="2">
         <v>3</v>
@@ -14150,12 +14143,12 @@
         <v>2</v>
       </c>
       <c r="AQ97" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="98" spans="1:43">
       <c r="A98" s="15" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B98" s="1">
         <v>46109</v>
@@ -14167,7 +14160,7 @@
         <v>28</v>
       </c>
       <c r="E98" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F98" s="3">
         <v>34.700000000000003</v>
@@ -14194,25 +14187,25 @@
         <v>0</v>
       </c>
       <c r="N98" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="O98" t="s">
+        <v>48</v>
+      </c>
+      <c r="P98" t="s">
         <v>49</v>
       </c>
-      <c r="P98" t="s">
+      <c r="Q98" t="s">
         <v>50</v>
-      </c>
-      <c r="Q98" t="s">
-        <v>51</v>
       </c>
       <c r="R98" s="2">
         <v>39</v>
       </c>
       <c r="S98" t="s">
+        <v>51</v>
+      </c>
+      <c r="T98" t="s">
         <v>52</v>
-      </c>
-      <c r="T98" t="s">
-        <v>53</v>
       </c>
       <c r="U98" s="2">
         <v>3</v>
@@ -14281,12 +14274,12 @@
         <v>2</v>
       </c>
       <c r="AQ98" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="99" spans="1:43">
       <c r="A99" s="15" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B99" s="1">
         <v>46109</v>
@@ -14298,7 +14291,7 @@
         <v>52</v>
       </c>
       <c r="E99" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F99" s="3">
         <v>23.5</v>
@@ -14325,25 +14318,25 @@
         <v>1</v>
       </c>
       <c r="N99" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O99" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="P99" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Q99" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="R99" s="2">
         <v>62</v>
       </c>
       <c r="S99" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T99" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="U99" s="2">
         <v>3</v>
@@ -14412,12 +14405,12 @@
         <v>2</v>
       </c>
       <c r="AQ99" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="100" spans="1:43">
       <c r="A100" s="15" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B100" s="1">
         <v>46108</v>
@@ -14429,7 +14422,7 @@
         <v>69</v>
       </c>
       <c r="E100" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F100" s="3">
         <v>35.1</v>
@@ -14456,25 +14449,25 @@
         <v>0</v>
       </c>
       <c r="N100" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O100" t="s">
+        <v>56</v>
+      </c>
+      <c r="P100" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q100" t="s">
         <v>57</v>
-      </c>
-      <c r="P100" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q100" t="s">
-        <v>58</v>
       </c>
       <c r="R100" s="2">
         <v>29</v>
       </c>
       <c r="S100" t="s">
+        <v>51</v>
+      </c>
+      <c r="T100" t="s">
         <v>52</v>
-      </c>
-      <c r="T100" t="s">
-        <v>53</v>
       </c>
       <c r="U100" s="2">
         <v>4</v>
@@ -14543,12 +14536,12 @@
         <v>2</v>
       </c>
       <c r="AQ100" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="101" spans="1:43">
       <c r="A101" s="16" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B101" s="17">
         <v>46109</v>
@@ -14560,7 +14553,7 @@
         <v>77</v>
       </c>
       <c r="E101" s="19" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F101" s="20">
         <v>29</v>
@@ -14587,25 +14580,25 @@
         <v>0</v>
       </c>
       <c r="N101" s="19" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O101" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="P101" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="P101" s="19" t="s">
-        <v>50</v>
-      </c>
       <c r="Q101" s="19" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="R101" s="18">
         <v>41</v>
       </c>
       <c r="S101" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="T101" s="19" t="s">
         <v>52</v>
-      </c>
-      <c r="T101" s="19" t="s">
-        <v>53</v>
       </c>
       <c r="U101" s="18">
         <v>3</v>
@@ -14674,7 +14667,7 @@
         <v>2</v>
       </c>
       <c r="AQ101" s="19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -14719,7 +14712,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="17.399999999999999">
       <c r="A1" s="22" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B1" s="23"/>
       <c r="C1" s="23"/>
@@ -14729,22 +14722,22 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="C3" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="D3" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="E3" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="F3" s="7" t="s">
         <v>179</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -14752,19 +14745,19 @@
         <v>0</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="D4" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="E4" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="F4" s="9" t="s">
         <v>184</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -14772,19 +14765,19 @@
         <v>1</v>
       </c>
       <c r="B5" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="D5" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="E5" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="F5" s="9" t="s">
         <v>189</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="27.6">
@@ -14792,19 +14785,19 @@
         <v>2</v>
       </c>
       <c r="B6" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="D6" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="F6" s="9" t="s">
         <v>192</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="27.6">
@@ -14812,19 +14805,19 @@
         <v>3</v>
       </c>
       <c r="B7" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="D7" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="D7" s="4" t="s">
+      <c r="E7" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="F7" s="9" t="s">
         <v>196</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="27.6">
@@ -14832,19 +14825,19 @@
         <v>4</v>
       </c>
       <c r="B8" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="D8" s="21" t="s">
         <v>198</v>
       </c>
-      <c r="C8" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="D8" s="21" t="s">
+      <c r="E8" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="F8" s="9" t="s">
         <v>200</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="27.6">
@@ -14852,19 +14845,19 @@
         <v>5</v>
       </c>
       <c r="B9" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="D9" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="C9" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="D9" s="4" t="s">
+      <c r="E9" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="F9" s="9" t="s">
         <v>204</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -14872,19 +14865,19 @@
         <v>6</v>
       </c>
       <c r="B10" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="D10" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="E10" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="F10" s="9" t="s">
         <v>209</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -14895,16 +14888,16 @@
         <v>7</v>
       </c>
       <c r="C11" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="D11" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="E11" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="E11" s="4" t="s">
-        <v>209</v>
-      </c>
       <c r="F11" s="9" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -14912,19 +14905,19 @@
         <v>8</v>
       </c>
       <c r="B12" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="F12" s="9" t="s">
         <v>212</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="F12" s="9" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -14932,19 +14925,19 @@
         <v>9</v>
       </c>
       <c r="B13" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="F13" s="9" t="s">
         <v>214</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="F13" s="9" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -14952,19 +14945,19 @@
         <v>10</v>
       </c>
       <c r="B14" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="D14" s="4" t="s">
         <v>216</v>
       </c>
-      <c r="C14" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="D14" s="4" t="s">
+      <c r="E14" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="F14" s="9" t="s">
         <v>218</v>
-      </c>
-      <c r="F14" s="9" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -14972,19 +14965,19 @@
         <v>11</v>
       </c>
       <c r="B15" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="F15" s="9" t="s">
         <v>220</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="F15" s="9" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -14992,19 +14985,19 @@
         <v>12</v>
       </c>
       <c r="B16" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="F16" s="9" t="s">
         <v>222</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="F16" s="9" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="27.6">
@@ -15012,19 +15005,19 @@
         <v>13</v>
       </c>
       <c r="B17" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="C17" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="D17" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="F17" s="9" t="s">
         <v>225</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>303</v>
-      </c>
-      <c r="F17" s="9" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -15032,19 +15025,19 @@
         <v>14</v>
       </c>
       <c r="B18" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="E18" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="C18" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="E18" s="4" t="s">
+      <c r="F18" s="9" t="s">
         <v>228</v>
-      </c>
-      <c r="F18" s="9" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -15052,19 +15045,19 @@
         <v>15</v>
       </c>
       <c r="B19" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="E19" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="C19" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="E19" s="4" t="s">
+      <c r="F19" s="9" t="s">
         <v>231</v>
-      </c>
-      <c r="F19" s="9" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="27.6">
@@ -15072,19 +15065,19 @@
         <v>16</v>
       </c>
       <c r="B20" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="E20" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="C20" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="E20" s="4" t="s">
+      <c r="F20" s="9" t="s">
         <v>234</v>
-      </c>
-      <c r="F20" s="9" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -15092,19 +15085,19 @@
         <v>17</v>
       </c>
       <c r="B21" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="E21" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="C21" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="E21" s="4" t="s">
+      <c r="F21" s="9" t="s">
         <v>237</v>
-      </c>
-      <c r="F21" s="9" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -15112,19 +15105,19 @@
         <v>19</v>
       </c>
       <c r="B22" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="E22" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="C22" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="E22" s="4" t="s">
+      <c r="F22" s="9" t="s">
         <v>240</v>
-      </c>
-      <c r="F22" s="9" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -15132,19 +15125,19 @@
         <v>20</v>
       </c>
       <c r="B23" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="C23" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="D23" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="E23" s="4" t="s">
         <v>243</v>
       </c>
-      <c r="D23" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="E23" s="4" t="s">
+      <c r="F23" s="9" t="s">
         <v>244</v>
-      </c>
-      <c r="F23" s="9" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -15152,19 +15145,19 @@
         <v>21</v>
       </c>
       <c r="B24" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="F24" s="9" t="s">
         <v>246</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="E24" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="F24" s="9" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -15172,19 +15165,19 @@
         <v>22</v>
       </c>
       <c r="B25" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="F25" s="9" t="s">
         <v>248</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="E25" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="F25" s="9" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -15192,19 +15185,19 @@
         <v>23</v>
       </c>
       <c r="B26" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="F26" s="9" t="s">
         <v>250</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="E26" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="F26" s="9" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -15212,19 +15205,19 @@
         <v>24</v>
       </c>
       <c r="B27" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="F27" s="9" t="s">
         <v>252</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="E27" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="F27" s="9" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -15232,19 +15225,19 @@
         <v>25</v>
       </c>
       <c r="B28" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="F28" s="9" t="s">
         <v>254</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="E28" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="F28" s="9" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -15252,19 +15245,19 @@
         <v>26</v>
       </c>
       <c r="B29" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="F29" s="9" t="s">
         <v>256</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="E29" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="F29" s="9" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -15272,19 +15265,19 @@
         <v>27</v>
       </c>
       <c r="B30" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="F30" s="9" t="s">
         <v>258</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="E30" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="F30" s="9" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -15292,19 +15285,19 @@
         <v>28</v>
       </c>
       <c r="B31" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="F31" s="9" t="s">
         <v>260</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="E31" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="F31" s="9" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -15312,19 +15305,19 @@
         <v>29</v>
       </c>
       <c r="B32" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="F32" s="9" t="s">
         <v>262</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="E32" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="F32" s="9" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -15332,19 +15325,19 @@
         <v>30</v>
       </c>
       <c r="B33" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="F33" s="9" t="s">
         <v>264</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="E33" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="F33" s="9" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -15352,19 +15345,19 @@
         <v>31</v>
       </c>
       <c r="B34" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="F34" s="9" t="s">
         <v>266</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="E34" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="F34" s="9" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -15372,19 +15365,19 @@
         <v>32</v>
       </c>
       <c r="B35" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="F35" s="9" t="s">
         <v>268</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="E35" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="F35" s="9" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -15392,19 +15385,19 @@
         <v>33</v>
       </c>
       <c r="B36" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="F36" s="9" t="s">
         <v>270</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="D36" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="E36" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="F36" s="9" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="27.6">
@@ -15412,19 +15405,19 @@
         <v>34</v>
       </c>
       <c r="B37" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="F37" s="9" t="s">
         <v>272</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="D37" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="E37" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="F37" s="9" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -15432,19 +15425,19 @@
         <v>35</v>
       </c>
       <c r="B38" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="E38" s="4" t="s">
         <v>274</v>
       </c>
-      <c r="C38" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="D38" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="E38" s="4" t="s">
+      <c r="F38" s="9" t="s">
         <v>275</v>
-      </c>
-      <c r="F38" s="9" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="27.6">
@@ -15452,19 +15445,19 @@
         <v>36</v>
       </c>
       <c r="B39" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="F39" s="9" t="s">
         <v>277</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="D39" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="E39" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="F39" s="9" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -15472,19 +15465,19 @@
         <v>37</v>
       </c>
       <c r="B40" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="F40" s="9" t="s">
         <v>279</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="D40" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="E40" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="F40" s="9" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -15492,19 +15485,19 @@
         <v>38</v>
       </c>
       <c r="B41" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="F41" s="9" t="s">
         <v>281</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="D41" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="E41" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="F41" s="9" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -15512,19 +15505,19 @@
         <v>39</v>
       </c>
       <c r="B42" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="E42" s="4" t="s">
         <v>283</v>
       </c>
-      <c r="C42" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="D42" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="E42" s="4" t="s">
+      <c r="F42" s="9" t="s">
         <v>284</v>
-      </c>
-      <c r="F42" s="9" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -15532,19 +15525,19 @@
         <v>40</v>
       </c>
       <c r="B43" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="F43" s="9" t="s">
         <v>286</v>
-      </c>
-      <c r="C43" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="D43" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="E43" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="F43" s="9" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -15552,19 +15545,19 @@
         <v>41</v>
       </c>
       <c r="B44" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="C44" s="4" t="s">
         <v>288</v>
       </c>
-      <c r="C44" s="4" t="s">
+      <c r="D44" s="21" t="s">
+        <v>198</v>
+      </c>
+      <c r="E44" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="D44" s="21" t="s">
-        <v>199</v>
-      </c>
-      <c r="E44" s="4" t="s">
+      <c r="F44" s="9" t="s">
         <v>290</v>
-      </c>
-      <c r="F44" s="9" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="27.6">
@@ -15572,79 +15565,79 @@
         <v>42</v>
       </c>
       <c r="B45" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="F45" s="9" t="s">
         <v>292</v>
-      </c>
-      <c r="C45" s="4" t="s">
-        <v>289</v>
-      </c>
-      <c r="D45" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="E45" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="F45" s="9" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="8" t="s">
-        <v>43</v>
+        <v>303</v>
       </c>
       <c r="B46" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="E46" s="4" t="s">
         <v>294</v>
       </c>
-      <c r="C46" s="4" t="s">
-        <v>289</v>
-      </c>
-      <c r="D46" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="E46" s="4" t="s">
+      <c r="F46" s="9" t="s">
         <v>295</v>
-      </c>
-      <c r="F46" s="9" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B47" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="E47" s="4" t="s">
         <v>297</v>
       </c>
-      <c r="C47" s="4" t="s">
-        <v>289</v>
-      </c>
-      <c r="D47" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="E47" s="4" t="s">
+      <c r="F47" s="9" t="s">
         <v>298</v>
-      </c>
-      <c r="F47" s="9" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="27.6">
       <c r="A48" s="10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B48" s="11" t="s">
+        <v>299</v>
+      </c>
+      <c r="C48" s="11" t="s">
+        <v>288</v>
+      </c>
+      <c r="D48" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="E48" s="11" t="s">
         <v>300</v>
       </c>
-      <c r="C48" s="11" t="s">
-        <v>289</v>
-      </c>
-      <c r="D48" s="11" t="s">
-        <v>183</v>
-      </c>
-      <c r="E48" s="11" t="s">
+      <c r="F48" s="12" t="s">
         <v>301</v>
-      </c>
-      <c r="F48" s="12" t="s">
-        <v>302</v>
       </c>
     </row>
   </sheetData>

--- a/hernia_followup_simulated_100_patients.xlsx
+++ b/hernia_followup_simulated_100_patients.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documentos\MASTER IA EN SANIDAD\TFM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{94D8681B-6FED-4CC1-8E24-D227196A79F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3BFA089-D095-4608-924F-6D046A17C996}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1220" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1220" uniqueCount="306">
   <si>
     <t>patient_id</t>
   </si>
@@ -946,6 +946,12 @@
   </si>
   <si>
     <t>risk_level</t>
+  </si>
+  <si>
+    <t>real_risk_level</t>
+  </si>
+  <si>
+    <t>real_suspected_complication</t>
   </si>
 </sst>
 </file>
@@ -1235,8 +1241,8 @@
     <tableColumn id="41" xr3:uid="{00000000-0010-0000-0000-000029000000}" name="unable_to_void"/>
     <tableColumn id="42" xr3:uid="{00000000-0010-0000-0000-00002A000000}" name="hours_without_voiding"/>
     <tableColumn id="43" xr3:uid="{00000000-0010-0000-0000-00002B000000}" name="suprapubic_pain"/>
-    <tableColumn id="47" xr3:uid="{00000000-0010-0000-0000-00002F000000}" name="risk_level"/>
-    <tableColumn id="48" xr3:uid="{00000000-0010-0000-0000-000030000000}" name="suspected_complication"/>
+    <tableColumn id="47" xr3:uid="{00000000-0010-0000-0000-00002F000000}" name="real_risk_level"/>
+    <tableColumn id="48" xr3:uid="{00000000-0010-0000-0000-000030000000}" name="real_suspected_complication"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1564,10 +1570,10 @@
         <v>40</v>
       </c>
       <c r="AP1" s="14" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AQ1" s="14" t="s">
-        <v>43</v>
+        <v>305</v>
       </c>
     </row>
     <row r="2" spans="1:43">
